--- a/backend/data/closed_acv.xlsx
+++ b/backend/data/closed_acv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gep1-my.sharepoint.com/personal/ajoseph_gep_com/Documents/Desktop/Project-Aether-Enterprise/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="8_{E886ED90-0776-4F81-A4C1-54B160D1665C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C41EE59-78BF-43D4-B557-E853C6CE1490}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="8_{E886ED90-0776-4F81-A4C1-54B160D1665C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53F42021-D1B9-4948-BEEF-0D806D122B17}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{362E1928-A501-4CAC-8243-2F29D3895462}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="closed_acv" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">closed_acv!$A$1:$R$598</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">closed_acv!$A$1:$R$612</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4819" uniqueCount="1371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4931" uniqueCount="1399">
   <si>
     <t>Closed_ACV_ID</t>
   </si>
@@ -2276,9 +2276,6 @@
     <t>Insulet Corporation</t>
   </si>
   <si>
-    <t>William Hoffman</t>
-  </si>
-  <si>
     <t>T1711</t>
   </si>
   <si>
@@ -4152,6 +4149,93 @@
   </si>
   <si>
     <t>NA Central Software</t>
+  </si>
+  <si>
+    <t>T2015</t>
+  </si>
+  <si>
+    <t>T2016</t>
+  </si>
+  <si>
+    <t>T2017</t>
+  </si>
+  <si>
+    <t>T2018</t>
+  </si>
+  <si>
+    <t>T2019</t>
+  </si>
+  <si>
+    <t>T2020</t>
+  </si>
+  <si>
+    <t>T2021</t>
+  </si>
+  <si>
+    <t>T2022</t>
+  </si>
+  <si>
+    <t>T2023</t>
+  </si>
+  <si>
+    <t>T2024</t>
+  </si>
+  <si>
+    <t>T2025</t>
+  </si>
+  <si>
+    <t>T2026</t>
+  </si>
+  <si>
+    <t>T2027</t>
+  </si>
+  <si>
+    <t>Zodiac/Fluidra - S2C License</t>
+  </si>
+  <si>
+    <t>Zodiac/Fluidra - S2C Implementation</t>
+  </si>
+  <si>
+    <t>KAPSARC - S2O License Fees</t>
+  </si>
+  <si>
+    <t>KAPSARC - S2O Implementation</t>
+  </si>
+  <si>
+    <t>ARADA - S2P Implementation Fees</t>
+  </si>
+  <si>
+    <t>TJX - CLM license</t>
+  </si>
+  <si>
+    <t>Caterpillar - Direct Global Go-Live Enhancement</t>
+  </si>
+  <si>
+    <t>Logitech - License Fees</t>
+  </si>
+  <si>
+    <t>Logitech - Implementation Fees</t>
+  </si>
+  <si>
+    <t>Masco - Quantum Migration Implementation</t>
+  </si>
+  <si>
+    <t>King Abdullah Petroleum Studies and Research Center</t>
+  </si>
+  <si>
+    <t>Logitech Europe S.A</t>
+  </si>
+  <si>
+    <t>CrossSell</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Johnson Fernandez</t>
+  </si>
+  <si>
+    <t>Bill Hoffman</t>
   </si>
 </sst>
 </file>
@@ -4638,13 +4722,16 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4690,7 +4777,28 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -5020,7 +5128,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445A7FF1-69C5-4B51-B3A2-42A65126DD1A}">
-  <dimension ref="A1:R598"/>
+  <dimension ref="A1:R612"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.54296875" style="5" bestFit="1" customWidth="1"/>
@@ -5239,7 +5347,7 @@
         <v>36</v>
       </c>
       <c r="R5" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -5280,7 +5388,7 @@
         <v>36</v>
       </c>
       <c r="R6" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
@@ -5435,7 +5543,7 @@
         <v>36</v>
       </c>
       <c r="R10" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
@@ -5640,7 +5748,7 @@
         <v>36</v>
       </c>
       <c r="R15" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
@@ -5722,7 +5830,7 @@
         <v>36</v>
       </c>
       <c r="R17" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
@@ -5763,7 +5871,7 @@
         <v>36</v>
       </c>
       <c r="R18" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
@@ -5804,7 +5912,7 @@
         <v>36</v>
       </c>
       <c r="R19" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
@@ -5845,7 +5953,7 @@
         <v>36</v>
       </c>
       <c r="R20" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
@@ -5927,7 +6035,7 @@
         <v>36</v>
       </c>
       <c r="R22" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.35">
@@ -6009,7 +6117,7 @@
         <v>36</v>
       </c>
       <c r="R24" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
@@ -6050,7 +6158,7 @@
         <v>36</v>
       </c>
       <c r="R25" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.35">
@@ -6410,7 +6518,7 @@
         <v>36</v>
       </c>
       <c r="R34" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.35">
@@ -6451,7 +6559,7 @@
         <v>36</v>
       </c>
       <c r="R35" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.35">
@@ -6530,7 +6638,7 @@
         <v>36</v>
       </c>
       <c r="R37" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.35">
@@ -6612,7 +6720,7 @@
         <v>36</v>
       </c>
       <c r="R39" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.35">
@@ -6650,7 +6758,7 @@
         <v>36</v>
       </c>
       <c r="R40" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.35">
@@ -7089,7 +7197,7 @@
         <v>36</v>
       </c>
       <c r="R51" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.35">
@@ -7130,7 +7238,7 @@
         <v>36</v>
       </c>
       <c r="R52" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.35">
@@ -7329,7 +7437,7 @@
         <v>36</v>
       </c>
       <c r="R57" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.35">
@@ -7367,7 +7475,7 @@
         <v>36</v>
       </c>
       <c r="R58" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.35">
@@ -7408,7 +7516,7 @@
         <v>36</v>
       </c>
       <c r="R59" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="60" spans="1:18" x14ac:dyDescent="0.35">
@@ -7531,7 +7639,7 @@
         <v>36</v>
       </c>
       <c r="R62" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.35">
@@ -7572,7 +7680,7 @@
         <v>36</v>
       </c>
       <c r="R63" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="64" spans="1:18" x14ac:dyDescent="0.35">
@@ -7613,7 +7721,7 @@
         <v>36</v>
       </c>
       <c r="R64" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.35">
@@ -7654,7 +7762,7 @@
         <v>36</v>
       </c>
       <c r="R65" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.35">
@@ -7692,7 +7800,7 @@
         <v>36</v>
       </c>
       <c r="R66" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.35">
@@ -7774,7 +7882,7 @@
         <v>36</v>
       </c>
       <c r="R68" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.35">
@@ -7815,7 +7923,7 @@
         <v>36</v>
       </c>
       <c r="R69" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.35">
@@ -7856,7 +7964,7 @@
         <v>36</v>
       </c>
       <c r="R70" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.35">
@@ -7897,7 +8005,7 @@
         <v>36</v>
       </c>
       <c r="R71" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.35">
@@ -7938,7 +8046,7 @@
         <v>36</v>
       </c>
       <c r="R72" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.35">
@@ -7979,7 +8087,7 @@
         <v>36</v>
       </c>
       <c r="R73" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.35">
@@ -8020,7 +8128,7 @@
         <v>36</v>
       </c>
       <c r="R74" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.35">
@@ -8061,7 +8169,7 @@
         <v>36</v>
       </c>
       <c r="R75" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.35">
@@ -8102,7 +8210,7 @@
         <v>36</v>
       </c>
       <c r="R76" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.35">
@@ -8225,7 +8333,7 @@
         <v>36</v>
       </c>
       <c r="R79" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.35">
@@ -8266,7 +8374,7 @@
         <v>36</v>
       </c>
       <c r="R80" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="81" spans="1:18" x14ac:dyDescent="0.35">
@@ -8538,7 +8646,7 @@
         <v>36</v>
       </c>
       <c r="R87" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="88" spans="1:18" x14ac:dyDescent="0.35">
@@ -8579,7 +8687,7 @@
         <v>36</v>
       </c>
       <c r="R88" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="89" spans="1:18" x14ac:dyDescent="0.35">
@@ -8740,7 +8848,7 @@
         <v>36</v>
       </c>
       <c r="R92" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="93" spans="1:18" x14ac:dyDescent="0.35">
@@ -8977,7 +9085,7 @@
         <v>36</v>
       </c>
       <c r="R98" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="99" spans="1:18" x14ac:dyDescent="0.35">
@@ -9018,7 +9126,7 @@
         <v>36</v>
       </c>
       <c r="R99" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.35">
@@ -9138,7 +9246,7 @@
         <v>36</v>
       </c>
       <c r="R102" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="103" spans="1:18" x14ac:dyDescent="0.35">
@@ -9220,7 +9328,7 @@
         <v>36</v>
       </c>
       <c r="R104" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="105" spans="1:18" x14ac:dyDescent="0.35">
@@ -9261,7 +9369,7 @@
         <v>36</v>
       </c>
       <c r="R105" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="106" spans="1:18" x14ac:dyDescent="0.35">
@@ -9419,7 +9527,7 @@
         <v>36</v>
       </c>
       <c r="R109" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.35">
@@ -9460,7 +9568,7 @@
         <v>36</v>
       </c>
       <c r="R110" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="111" spans="1:18" x14ac:dyDescent="0.35">
@@ -9501,7 +9609,7 @@
         <v>36</v>
       </c>
       <c r="R111" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="112" spans="1:18" x14ac:dyDescent="0.35">
@@ -9542,7 +9650,7 @@
         <v>36</v>
       </c>
       <c r="R112" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="113" spans="1:18" x14ac:dyDescent="0.35">
@@ -9621,7 +9729,7 @@
         <v>36</v>
       </c>
       <c r="R114" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="115" spans="1:18" x14ac:dyDescent="0.35">
@@ -9662,7 +9770,7 @@
         <v>36</v>
       </c>
       <c r="R115" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="116" spans="1:18" x14ac:dyDescent="0.35">
@@ -9978,7 +10086,7 @@
         <v>36</v>
       </c>
       <c r="R123" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="124" spans="1:18" x14ac:dyDescent="0.35">
@@ -10019,7 +10127,7 @@
         <v>36</v>
       </c>
       <c r="R124" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="125" spans="1:18" x14ac:dyDescent="0.35">
@@ -10060,7 +10168,7 @@
         <v>36</v>
       </c>
       <c r="R125" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="126" spans="1:18" x14ac:dyDescent="0.35">
@@ -10224,7 +10332,7 @@
         <v>36</v>
       </c>
       <c r="R129" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="130" spans="1:18" x14ac:dyDescent="0.35">
@@ -10265,7 +10373,7 @@
         <v>36</v>
       </c>
       <c r="R130" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="131" spans="1:18" x14ac:dyDescent="0.35">
@@ -10306,7 +10414,7 @@
         <v>36</v>
       </c>
       <c r="R131" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="132" spans="1:18" x14ac:dyDescent="0.35">
@@ -10347,7 +10455,7 @@
         <v>36</v>
       </c>
       <c r="R132" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="133" spans="1:18" x14ac:dyDescent="0.35">
@@ -10388,7 +10496,7 @@
         <v>36</v>
       </c>
       <c r="R133" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.35">
@@ -10429,7 +10537,7 @@
         <v>36</v>
       </c>
       <c r="R134" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="135" spans="1:18" x14ac:dyDescent="0.35">
@@ -10587,7 +10695,7 @@
         <v>36</v>
       </c>
       <c r="R138" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="139" spans="1:18" x14ac:dyDescent="0.35">
@@ -10628,7 +10736,7 @@
         <v>36</v>
       </c>
       <c r="R139" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="140" spans="1:18" x14ac:dyDescent="0.35">
@@ -10669,7 +10777,7 @@
         <v>36</v>
       </c>
       <c r="R140" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="141" spans="1:18" x14ac:dyDescent="0.35">
@@ -11102,7 +11210,7 @@
         <v>36</v>
       </c>
       <c r="R151" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="152" spans="1:18" x14ac:dyDescent="0.35">
@@ -11143,7 +11251,7 @@
         <v>36</v>
       </c>
       <c r="R152" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="153" spans="1:18" x14ac:dyDescent="0.35">
@@ -11184,7 +11292,7 @@
         <v>36</v>
       </c>
       <c r="R153" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="154" spans="1:18" x14ac:dyDescent="0.35">
@@ -11222,7 +11330,7 @@
         <v>36</v>
       </c>
       <c r="R154" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="155" spans="1:18" x14ac:dyDescent="0.35">
@@ -11421,7 +11529,7 @@
         <v>36</v>
       </c>
       <c r="R159" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="160" spans="1:18" x14ac:dyDescent="0.35">
@@ -11462,7 +11570,7 @@
         <v>36</v>
       </c>
       <c r="R160" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="161" spans="1:18" x14ac:dyDescent="0.35">
@@ -11503,7 +11611,7 @@
         <v>36</v>
       </c>
       <c r="R161" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="162" spans="1:18" x14ac:dyDescent="0.35">
@@ -11544,7 +11652,7 @@
         <v>36</v>
       </c>
       <c r="R162" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="163" spans="1:18" x14ac:dyDescent="0.35">
@@ -11705,7 +11813,7 @@
         <v>36</v>
       </c>
       <c r="R166" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.35">
@@ -11746,7 +11854,7 @@
         <v>36</v>
       </c>
       <c r="R167" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.35">
@@ -11825,7 +11933,7 @@
         <v>36</v>
       </c>
       <c r="R169" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.35">
@@ -12021,7 +12129,7 @@
         <v>36</v>
       </c>
       <c r="R174" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="175" spans="1:18" x14ac:dyDescent="0.35">
@@ -12062,7 +12170,7 @@
         <v>36</v>
       </c>
       <c r="R175" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="176" spans="1:18" x14ac:dyDescent="0.35">
@@ -12185,7 +12293,7 @@
         <v>36</v>
       </c>
       <c r="R178" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="179" spans="1:18" x14ac:dyDescent="0.35">
@@ -12308,7 +12416,7 @@
         <v>36</v>
       </c>
       <c r="R181" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.35">
@@ -12349,7 +12457,7 @@
         <v>36</v>
       </c>
       <c r="R182" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.35">
@@ -12390,7 +12498,7 @@
         <v>36</v>
       </c>
       <c r="R183" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="184" spans="1:18" x14ac:dyDescent="0.35">
@@ -12472,7 +12580,7 @@
         <v>36</v>
       </c>
       <c r="R185" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="186" spans="1:18" x14ac:dyDescent="0.35">
@@ -12668,7 +12776,7 @@
         <v>36</v>
       </c>
       <c r="R190" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="191" spans="1:18" x14ac:dyDescent="0.35">
@@ -12709,7 +12817,7 @@
         <v>36</v>
       </c>
       <c r="R191" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="192" spans="1:18" x14ac:dyDescent="0.35">
@@ -12873,7 +12981,7 @@
         <v>36</v>
       </c>
       <c r="R195" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="196" spans="1:18" x14ac:dyDescent="0.35">
@@ -12914,7 +13022,7 @@
         <v>36</v>
       </c>
       <c r="R196" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="197" spans="1:18" x14ac:dyDescent="0.35">
@@ -12955,7 +13063,7 @@
         <v>36</v>
       </c>
       <c r="R197" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="198" spans="1:18" x14ac:dyDescent="0.35">
@@ -13034,7 +13142,7 @@
         <v>36</v>
       </c>
       <c r="R199" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="200" spans="1:18" x14ac:dyDescent="0.35">
@@ -13189,7 +13297,7 @@
         <v>36</v>
       </c>
       <c r="R203" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="204" spans="1:18" x14ac:dyDescent="0.35">
@@ -13350,7 +13458,7 @@
         <v>36</v>
       </c>
       <c r="R207" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="208" spans="1:18" x14ac:dyDescent="0.35">
@@ -13432,7 +13540,7 @@
         <v>36</v>
       </c>
       <c r="R209" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="210" spans="1:18" x14ac:dyDescent="0.35">
@@ -13511,7 +13619,7 @@
         <v>36</v>
       </c>
       <c r="R211" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="212" spans="1:18" x14ac:dyDescent="0.35">
@@ -13634,7 +13742,7 @@
         <v>36</v>
       </c>
       <c r="R214" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.35">
@@ -13754,7 +13862,7 @@
         <v>36</v>
       </c>
       <c r="R217" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="218" spans="1:18" x14ac:dyDescent="0.35">
@@ -13950,7 +14058,7 @@
         <v>36</v>
       </c>
       <c r="R222" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="223" spans="1:18" x14ac:dyDescent="0.35">
@@ -14152,7 +14260,7 @@
         <v>36</v>
       </c>
       <c r="R227" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="228" spans="1:18" x14ac:dyDescent="0.35">
@@ -14272,7 +14380,7 @@
         <v>36</v>
       </c>
       <c r="R230" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="231" spans="1:18" x14ac:dyDescent="0.35">
@@ -14752,7 +14860,7 @@
         <v>36</v>
       </c>
       <c r="R242" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="243" spans="1:18" x14ac:dyDescent="0.35">
@@ -15393,7 +15501,7 @@
         <v>36</v>
       </c>
       <c r="R258" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="259" spans="1:18" x14ac:dyDescent="0.35">
@@ -15551,7 +15659,7 @@
         <v>36</v>
       </c>
       <c r="R262" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="263" spans="1:18" x14ac:dyDescent="0.35">
@@ -15592,7 +15700,7 @@
         <v>36</v>
       </c>
       <c r="R263" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="264" spans="1:18" x14ac:dyDescent="0.35">
@@ -15633,7 +15741,7 @@
         <v>36</v>
       </c>
       <c r="R264" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="265" spans="1:18" x14ac:dyDescent="0.35">
@@ -15674,7 +15782,7 @@
         <v>36</v>
       </c>
       <c r="R265" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="266" spans="1:18" x14ac:dyDescent="0.35">
@@ -15753,7 +15861,7 @@
         <v>36</v>
       </c>
       <c r="R267" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="268" spans="1:18" x14ac:dyDescent="0.35">
@@ -15794,7 +15902,7 @@
         <v>36</v>
       </c>
       <c r="R268" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="269" spans="1:18" x14ac:dyDescent="0.35">
@@ -15911,7 +16019,7 @@
         <v>36</v>
       </c>
       <c r="R271" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="272" spans="1:18" x14ac:dyDescent="0.35">
@@ -16075,7 +16183,7 @@
         <v>36</v>
       </c>
       <c r="R275" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="276" spans="1:18" x14ac:dyDescent="0.35">
@@ -16116,7 +16224,7 @@
         <v>36</v>
       </c>
       <c r="R276" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="277" spans="1:18" x14ac:dyDescent="0.35">
@@ -16470,7 +16578,7 @@
         <v>36</v>
       </c>
       <c r="R285" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="286" spans="1:18" x14ac:dyDescent="0.35">
@@ -16587,7 +16695,7 @@
         <v>36</v>
       </c>
       <c r="R288" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="289" spans="1:18" x14ac:dyDescent="0.35">
@@ -16625,7 +16733,7 @@
         <v>36</v>
       </c>
       <c r="R289" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="290" spans="1:18" x14ac:dyDescent="0.35">
@@ -16707,7 +16815,7 @@
         <v>36</v>
       </c>
       <c r="R291" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="292" spans="1:18" x14ac:dyDescent="0.35">
@@ -16748,7 +16856,7 @@
         <v>36</v>
       </c>
       <c r="R292" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="293" spans="1:18" x14ac:dyDescent="0.35">
@@ -16789,7 +16897,7 @@
         <v>36</v>
       </c>
       <c r="R293" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="294" spans="1:18" x14ac:dyDescent="0.35">
@@ -16868,7 +16976,7 @@
         <v>36</v>
       </c>
       <c r="R295" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="296" spans="1:18" x14ac:dyDescent="0.35">
@@ -16941,7 +17049,7 @@
         <v>155000</v>
       </c>
       <c r="O297" t="s">
-        <v>745</v>
+        <v>1398</v>
       </c>
       <c r="P297">
         <v>3337</v>
@@ -16950,15 +17058,15 @@
         <v>36</v>
       </c>
       <c r="R297" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="298" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
+        <v>745</v>
+      </c>
+      <c r="C298" t="s">
         <v>746</v>
-      </c>
-      <c r="C298" t="s">
-        <v>747</v>
       </c>
       <c r="D298" t="s">
         <v>744</v>
@@ -16979,7 +17087,7 @@
         <v>165000</v>
       </c>
       <c r="O298" t="s">
-        <v>745</v>
+        <v>1398</v>
       </c>
       <c r="P298">
         <v>3338</v>
@@ -16988,21 +17096,21 @@
         <v>36</v>
       </c>
       <c r="R298" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="299" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B299" s="5">
         <v>308073979088</v>
       </c>
       <c r="C299" t="s">
+        <v>748</v>
+      </c>
+      <c r="D299" t="s">
         <v>749</v>
-      </c>
-      <c r="D299" t="s">
-        <v>750</v>
       </c>
       <c r="E299" s="1">
         <v>45627</v>
@@ -17029,12 +17137,12 @@
         <v>36</v>
       </c>
       <c r="R299" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="300" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B300" s="5">
         <v>308157141186</v>
@@ -17070,21 +17178,21 @@
         <v>36</v>
       </c>
       <c r="R300" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="301" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B301" s="5">
         <v>308084621526</v>
       </c>
       <c r="C301" t="s">
+        <v>752</v>
+      </c>
+      <c r="D301" t="s">
         <v>753</v>
-      </c>
-      <c r="D301" t="s">
-        <v>754</v>
       </c>
       <c r="E301" s="1">
         <v>45627</v>
@@ -17102,7 +17210,7 @@
         <v>159600</v>
       </c>
       <c r="O301" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="P301">
         <v>3344</v>
@@ -17111,21 +17219,21 @@
         <v>36</v>
       </c>
       <c r="R301" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="302" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B302" s="5">
         <v>308084621526</v>
       </c>
       <c r="C302" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D302" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E302" s="1">
         <v>45627</v>
@@ -17143,7 +17251,7 @@
         <v>189000</v>
       </c>
       <c r="O302" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="P302">
         <v>3345</v>
@@ -17152,21 +17260,21 @@
         <v>36</v>
       </c>
       <c r="R302" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="303" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B303" s="5">
         <v>308073981132</v>
       </c>
       <c r="C303" t="s">
+        <v>758</v>
+      </c>
+      <c r="D303" t="s">
         <v>759</v>
-      </c>
-      <c r="D303" t="s">
-        <v>760</v>
       </c>
       <c r="E303" s="1">
         <v>45627</v>
@@ -17193,21 +17301,21 @@
         <v>36</v>
       </c>
       <c r="R303" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="304" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B304" s="5">
         <v>308156237007</v>
       </c>
       <c r="C304" t="s">
+        <v>761</v>
+      </c>
+      <c r="D304" t="s">
         <v>762</v>
-      </c>
-      <c r="D304" t="s">
-        <v>763</v>
       </c>
       <c r="E304" s="1">
         <v>45627</v>
@@ -17234,21 +17342,21 @@
         <v>36</v>
       </c>
       <c r="R304" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="305" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B305" s="5">
         <v>308000370914</v>
       </c>
       <c r="C305" t="s">
+        <v>764</v>
+      </c>
+      <c r="D305" t="s">
         <v>765</v>
-      </c>
-      <c r="D305" t="s">
-        <v>766</v>
       </c>
       <c r="E305" s="1">
         <v>45627</v>
@@ -17266,7 +17374,7 @@
         <v>325000</v>
       </c>
       <c r="O305" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="P305">
         <v>3351</v>
@@ -17275,21 +17383,21 @@
         <v>36</v>
       </c>
       <c r="R305" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="306" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B306" s="5">
         <v>308000370914</v>
       </c>
       <c r="C306" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D306" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E306" s="1">
         <v>45627</v>
@@ -17307,7 +17415,7 @@
         <v>650000</v>
       </c>
       <c r="O306" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="P306">
         <v>3352</v>
@@ -17316,21 +17424,21 @@
         <v>36</v>
       </c>
       <c r="R306" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="307" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B307" s="5">
         <v>308190614734</v>
       </c>
       <c r="C307" t="s">
+        <v>770</v>
+      </c>
+      <c r="D307" t="s">
         <v>771</v>
-      </c>
-      <c r="D307" t="s">
-        <v>772</v>
       </c>
       <c r="E307" s="1">
         <v>45627</v>
@@ -17348,7 +17456,7 @@
         <v>164727.4559</v>
       </c>
       <c r="O307" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P307">
         <v>3353</v>
@@ -17357,21 +17465,21 @@
         <v>36</v>
       </c>
       <c r="R307" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="308" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B308" s="5">
         <v>308156991735</v>
       </c>
       <c r="C308" t="s">
+        <v>774</v>
+      </c>
+      <c r="D308" t="s">
         <v>775</v>
-      </c>
-      <c r="D308" t="s">
-        <v>776</v>
       </c>
       <c r="E308" s="1">
         <v>45627</v>
@@ -17398,12 +17506,12 @@
         <v>36</v>
       </c>
       <c r="R308" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="309" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B309" s="5">
         <v>308000373964</v>
@@ -17444,16 +17552,16 @@
     </row>
     <row r="310" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B310" s="5">
         <v>308156240114</v>
       </c>
       <c r="C310" t="s">
+        <v>778</v>
+      </c>
+      <c r="D310" t="s">
         <v>779</v>
-      </c>
-      <c r="D310" t="s">
-        <v>780</v>
       </c>
       <c r="E310" s="1">
         <v>45627</v>
@@ -17485,16 +17593,16 @@
     </row>
     <row r="311" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B311" s="5">
         <v>308156774586</v>
       </c>
       <c r="C311" t="s">
+        <v>781</v>
+      </c>
+      <c r="D311" t="s">
         <v>782</v>
-      </c>
-      <c r="D311" t="s">
-        <v>783</v>
       </c>
       <c r="E311" s="1">
         <v>45627</v>
@@ -17512,7 +17620,7 @@
         <v>24570</v>
       </c>
       <c r="O311" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P311">
         <v>3357</v>
@@ -17526,16 +17634,16 @@
     </row>
     <row r="312" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B312" s="5">
         <v>308156774586</v>
       </c>
       <c r="C312" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D312" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E312" s="1">
         <v>45627</v>
@@ -17553,7 +17661,7 @@
         <v>5250</v>
       </c>
       <c r="O312" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="P312">
         <v>3358</v>
@@ -17567,7 +17675,7 @@
     </row>
     <row r="313" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C313" t="s">
         <v>613</v>
@@ -17605,13 +17713,13 @@
     </row>
     <row r="314" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
+        <v>787</v>
+      </c>
+      <c r="C314" t="s">
         <v>788</v>
       </c>
-      <c r="C314" t="s">
+      <c r="D314" t="s">
         <v>789</v>
-      </c>
-      <c r="D314" t="s">
-        <v>790</v>
       </c>
       <c r="E314" s="1">
         <v>45627</v>
@@ -17643,7 +17751,7 @@
     </row>
     <row r="315" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C315" t="s">
         <v>29</v>
@@ -17681,10 +17789,10 @@
     </row>
     <row r="316" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
+        <v>791</v>
+      </c>
+      <c r="C316" t="s">
         <v>792</v>
-      </c>
-      <c r="C316" t="s">
-        <v>793</v>
       </c>
       <c r="D316" t="s">
         <v>403</v>
@@ -17719,16 +17827,16 @@
     </row>
     <row r="317" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
+        <v>793</v>
+      </c>
+      <c r="B317" s="5" t="s">
         <v>794</v>
       </c>
-      <c r="B317" s="5" t="s">
+      <c r="C317" t="s">
         <v>795</v>
       </c>
-      <c r="C317" t="s">
+      <c r="D317" t="s">
         <v>796</v>
-      </c>
-      <c r="D317" t="s">
-        <v>797</v>
       </c>
       <c r="E317" s="1">
         <v>45627</v>
@@ -17746,7 +17854,7 @@
         <v>17500</v>
       </c>
       <c r="O317" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="P317">
         <v>3375</v>
@@ -17760,13 +17868,13 @@
     </row>
     <row r="318" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B318" s="5">
         <v>308073980141</v>
       </c>
       <c r="C318" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D318" t="s">
         <v>445</v>
@@ -17801,7 +17909,7 @@
     </row>
     <row r="319" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C319" t="s">
         <v>286</v>
@@ -17839,13 +17947,13 @@
     </row>
     <row r="320" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B320" s="5">
         <v>308157141208</v>
       </c>
       <c r="C320" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D320" t="s">
         <v>298</v>
@@ -17875,12 +17983,12 @@
         <v>36</v>
       </c>
       <c r="R320" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="321" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C321" t="s">
         <v>187</v>
@@ -17918,13 +18026,13 @@
     </row>
     <row r="322" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
+        <v>804</v>
+      </c>
+      <c r="C322" t="s">
         <v>805</v>
       </c>
-      <c r="C322" t="s">
+      <c r="D322" t="s">
         <v>806</v>
-      </c>
-      <c r="D322" t="s">
-        <v>807</v>
       </c>
       <c r="E322" s="1">
         <v>45658</v>
@@ -17956,7 +18064,7 @@
     </row>
     <row r="323" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B323" s="5">
         <v>308156452053</v>
@@ -17997,7 +18105,7 @@
     </row>
     <row r="324" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B324" s="5">
         <v>308156774647</v>
@@ -18038,7 +18146,7 @@
     </row>
     <row r="325" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C325" t="s">
         <v>397</v>
@@ -18076,7 +18184,7 @@
     </row>
     <row r="326" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B326" s="5">
         <v>308156243146</v>
@@ -18117,16 +18225,16 @@
     </row>
     <row r="327" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B327" s="5">
         <v>308102565054</v>
       </c>
       <c r="C327" t="s">
+        <v>812</v>
+      </c>
+      <c r="D327" t="s">
         <v>813</v>
-      </c>
-      <c r="D327" t="s">
-        <v>814</v>
       </c>
       <c r="E327" s="1">
         <v>45658</v>
@@ -18144,7 +18252,7 @@
         <v>44444</v>
       </c>
       <c r="O327" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="P327">
         <v>3388</v>
@@ -18153,21 +18261,21 @@
         <v>36</v>
       </c>
       <c r="R327" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="328" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B328" s="5">
         <v>308102565054</v>
       </c>
       <c r="C328" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D328" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E328" s="1">
         <v>45658</v>
@@ -18185,7 +18293,7 @@
         <v>52222</v>
       </c>
       <c r="O328" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="P328">
         <v>3387</v>
@@ -18194,15 +18302,15 @@
         <v>36</v>
       </c>
       <c r="R328" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="329" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
+        <v>817</v>
+      </c>
+      <c r="C329" t="s">
         <v>818</v>
-      </c>
-      <c r="C329" t="s">
-        <v>819</v>
       </c>
       <c r="D329" t="s">
         <v>403</v>
@@ -18237,7 +18345,7 @@
     </row>
     <row r="330" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B330" s="5">
         <v>308156612841</v>
@@ -18273,12 +18381,12 @@
         <v>36</v>
       </c>
       <c r="R330" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="331" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C331" t="s">
         <v>349</v>
@@ -18316,16 +18424,16 @@
     </row>
     <row r="332" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B332" s="5">
         <v>308157293771</v>
       </c>
       <c r="C332" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D332" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E332" s="1">
         <v>45689</v>
@@ -18352,12 +18460,12 @@
         <v>36</v>
       </c>
       <c r="R332" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="333" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C333" t="s">
         <v>387</v>
@@ -18395,16 +18503,16 @@
     </row>
     <row r="334" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B334" s="5">
         <v>308156237007</v>
       </c>
       <c r="C334" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D334" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E334" s="1">
         <v>45689</v>
@@ -18431,18 +18539,18 @@
         <v>36</v>
       </c>
       <c r="R334" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="335" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B335" s="5">
         <v>308156990661</v>
       </c>
       <c r="C335" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D335" t="s">
         <v>113</v>
@@ -18477,16 +18585,16 @@
     </row>
     <row r="336" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B336" s="5">
         <v>308003947719</v>
       </c>
       <c r="C336" t="s">
+        <v>829</v>
+      </c>
+      <c r="D336" t="s">
         <v>830</v>
-      </c>
-      <c r="D336" t="s">
-        <v>831</v>
       </c>
       <c r="E336" s="1">
         <v>45689</v>
@@ -18513,21 +18621,21 @@
         <v>36</v>
       </c>
       <c r="R336" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="337" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B337" s="5">
         <v>308003947719</v>
       </c>
       <c r="C337" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D337" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E337" s="1">
         <v>45689</v>
@@ -18554,18 +18662,18 @@
         <v>36</v>
       </c>
       <c r="R337" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="338" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B338" s="5">
         <v>308156995795</v>
       </c>
       <c r="C338" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D338" t="s">
         <v>188</v>
@@ -18600,7 +18708,7 @@
     </row>
     <row r="339" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C339" t="s">
         <v>243</v>
@@ -18638,7 +18746,7 @@
     </row>
     <row r="340" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C340" t="s">
         <v>286</v>
@@ -18676,7 +18784,7 @@
     </row>
     <row r="341" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C341" t="s">
         <v>313</v>
@@ -18714,16 +18822,16 @@
     </row>
     <row r="342" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B342" s="5">
         <v>308000370887</v>
       </c>
       <c r="C342" t="s">
+        <v>839</v>
+      </c>
+      <c r="D342" t="s">
         <v>840</v>
-      </c>
-      <c r="D342" t="s">
-        <v>841</v>
       </c>
       <c r="E342" s="1">
         <v>45689</v>
@@ -18750,21 +18858,21 @@
         <v>36</v>
       </c>
       <c r="R342" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="343" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B343" s="5">
         <v>308000370887</v>
       </c>
       <c r="C343" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D343" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E343" s="1">
         <v>45689</v>
@@ -18791,21 +18899,21 @@
         <v>36</v>
       </c>
       <c r="R343" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="344" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B344" s="5">
         <v>308157138156</v>
       </c>
       <c r="C344" t="s">
+        <v>844</v>
+      </c>
+      <c r="D344" t="s">
         <v>845</v>
-      </c>
-      <c r="D344" t="s">
-        <v>846</v>
       </c>
       <c r="E344" s="1">
         <v>45717</v>
@@ -18832,21 +18940,21 @@
         <v>36</v>
       </c>
       <c r="R344" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="345" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B345" s="5">
         <v>308157138156</v>
       </c>
       <c r="C345" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D345" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E345" s="1">
         <v>45717</v>
@@ -18873,15 +18981,15 @@
         <v>36</v>
       </c>
       <c r="R345" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="346" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C346" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D346" t="s">
         <v>403</v>
@@ -18916,13 +19024,13 @@
     </row>
     <row r="347" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B347" s="5">
         <v>308190614732</v>
       </c>
       <c r="C347" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D347" t="s">
         <v>123</v>
@@ -18957,13 +19065,13 @@
     </row>
     <row r="348" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B348" s="5">
         <v>308190614732</v>
       </c>
       <c r="C348" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="D348" t="s">
         <v>123</v>
@@ -18998,7 +19106,7 @@
     </row>
     <row r="349" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B349" s="5">
         <v>308073981169</v>
@@ -19039,16 +19147,16 @@
     </row>
     <row r="350" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B350" s="5">
         <v>308157290729</v>
       </c>
       <c r="C350" t="s">
+        <v>855</v>
+      </c>
+      <c r="D350" t="s">
         <v>856</v>
-      </c>
-      <c r="D350" t="s">
-        <v>857</v>
       </c>
       <c r="E350" s="1">
         <v>45717</v>
@@ -19075,21 +19183,21 @@
         <v>36</v>
       </c>
       <c r="R350" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="351" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B351" s="5">
         <v>308157290729</v>
       </c>
       <c r="C351" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="D351" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E351" s="1">
         <v>45717</v>
@@ -19116,18 +19224,18 @@
         <v>36</v>
       </c>
       <c r="R351" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="352" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B352" s="5">
         <v>308156612810</v>
       </c>
       <c r="C352" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D352" t="s">
         <v>258</v>
@@ -19162,13 +19270,13 @@
     </row>
     <row r="353" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B353" s="5">
         <v>308156612810</v>
       </c>
       <c r="C353" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D353" t="s">
         <v>258</v>
@@ -19203,7 +19311,7 @@
     </row>
     <row r="354" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C354" t="s">
         <v>397</v>
@@ -19241,16 +19349,16 @@
     </row>
     <row r="355" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B355" s="5">
         <v>308156451039</v>
       </c>
       <c r="C355" t="s">
+        <v>865</v>
+      </c>
+      <c r="D355" t="s">
         <v>866</v>
-      </c>
-      <c r="D355" t="s">
-        <v>867</v>
       </c>
       <c r="E355" s="1">
         <v>45717</v>
@@ -19277,21 +19385,21 @@
         <v>36</v>
       </c>
       <c r="R355" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="356" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B356" s="5">
         <v>308156451039</v>
       </c>
       <c r="C356" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D356" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E356" s="1">
         <v>45717</v>
@@ -19318,21 +19426,21 @@
         <v>36</v>
       </c>
       <c r="R356" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="357" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B357" s="5">
         <v>308190614734</v>
       </c>
       <c r="C357" t="s">
+        <v>870</v>
+      </c>
+      <c r="D357" t="s">
         <v>871</v>
-      </c>
-      <c r="D357" t="s">
-        <v>872</v>
       </c>
       <c r="E357" s="1">
         <v>45717</v>
@@ -19359,18 +19467,18 @@
         <v>36</v>
       </c>
       <c r="R357" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="358" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B358" s="5">
         <v>308156615907</v>
       </c>
       <c r="C358" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D358" t="s">
         <v>736</v>
@@ -19400,12 +19508,12 @@
         <v>36</v>
       </c>
       <c r="R358" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="359" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B359" s="5">
         <v>308156775630</v>
@@ -19441,12 +19549,12 @@
         <v>36</v>
       </c>
       <c r="R359" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="360" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B360" s="5">
         <v>308084622557</v>
@@ -19487,7 +19595,7 @@
     </row>
     <row r="361" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C361" t="s">
         <v>164</v>
@@ -19525,16 +19633,16 @@
     </row>
     <row r="362" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B362" s="5">
         <v>308000370879</v>
       </c>
       <c r="C362" t="s">
+        <v>878</v>
+      </c>
+      <c r="D362" t="s">
         <v>879</v>
-      </c>
-      <c r="D362" t="s">
-        <v>880</v>
       </c>
       <c r="E362" s="1">
         <v>45717</v>
@@ -19561,21 +19669,21 @@
         <v>36</v>
       </c>
       <c r="R362" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="363" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B363" s="5">
         <v>308000370879</v>
       </c>
       <c r="C363" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D363" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="E363" s="1">
         <v>45717</v>
@@ -19602,21 +19710,21 @@
         <v>36</v>
       </c>
       <c r="R363" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="364" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B364" s="5">
         <v>308156243142</v>
       </c>
       <c r="C364" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D364" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E364" s="1">
         <v>45717</v>
@@ -19643,12 +19751,12 @@
         <v>36</v>
       </c>
       <c r="R364" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="365" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B365" s="5">
         <v>308152809716</v>
@@ -19689,16 +19797,16 @@
     </row>
     <row r="366" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B366" s="5">
         <v>308157141226</v>
       </c>
       <c r="C366" t="s">
+        <v>886</v>
+      </c>
+      <c r="D366" t="s">
         <v>887</v>
-      </c>
-      <c r="D366" t="s">
-        <v>888</v>
       </c>
       <c r="E366" s="1">
         <v>45717</v>
@@ -19730,7 +19838,7 @@
     </row>
     <row r="367" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B367" s="5">
         <v>308157293775</v>
@@ -19771,7 +19879,7 @@
     </row>
     <row r="368" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B368" s="5">
         <v>308190614719</v>
@@ -19807,21 +19915,21 @@
         <v>36</v>
       </c>
       <c r="R368" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="369" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B369" s="5">
         <v>308156239071</v>
       </c>
       <c r="C369" t="s">
+        <v>891</v>
+      </c>
+      <c r="D369" t="s">
         <v>892</v>
-      </c>
-      <c r="D369" t="s">
-        <v>893</v>
       </c>
       <c r="E369" s="1">
         <v>45717</v>
@@ -19848,21 +19956,21 @@
         <v>36</v>
       </c>
       <c r="R369" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="370" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B370" s="5">
         <v>308156239071</v>
       </c>
       <c r="C370" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D370" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E370" s="1">
         <v>45717</v>
@@ -19889,21 +19997,21 @@
         <v>36</v>
       </c>
       <c r="R370" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="371" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B371" s="5">
         <v>308156774635</v>
       </c>
       <c r="C371" t="s">
+        <v>896</v>
+      </c>
+      <c r="D371" t="s">
         <v>897</v>
-      </c>
-      <c r="D371" t="s">
-        <v>898</v>
       </c>
       <c r="E371" s="1">
         <v>45717</v>
@@ -19930,21 +20038,21 @@
         <v>36</v>
       </c>
       <c r="R371" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="372" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B372" s="5">
         <v>308156774635</v>
       </c>
       <c r="C372" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D372" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E372" s="1">
         <v>45717</v>
@@ -19971,18 +20079,18 @@
         <v>36</v>
       </c>
       <c r="R372" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="373" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
+        <v>900</v>
+      </c>
+      <c r="B373" s="5" t="s">
         <v>901</v>
       </c>
-      <c r="B373" s="5" t="s">
+      <c r="C373" t="s">
         <v>902</v>
-      </c>
-      <c r="C373" t="s">
-        <v>903</v>
       </c>
       <c r="D373" t="s">
         <v>307</v>
@@ -20017,13 +20125,13 @@
     </row>
     <row r="374" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
+        <v>903</v>
+      </c>
+      <c r="C374" t="s">
         <v>904</v>
       </c>
-      <c r="C374" t="s">
+      <c r="D374" t="s">
         <v>905</v>
-      </c>
-      <c r="D374" t="s">
-        <v>906</v>
       </c>
       <c r="E374" s="1">
         <v>45717</v>
@@ -20055,16 +20163,16 @@
     </row>
     <row r="375" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
+        <v>906</v>
+      </c>
+      <c r="B375" s="5" t="s">
         <v>907</v>
       </c>
-      <c r="B375" s="5" t="s">
+      <c r="C375" t="s">
         <v>908</v>
       </c>
-      <c r="C375" t="s">
+      <c r="D375" t="s">
         <v>909</v>
-      </c>
-      <c r="D375" t="s">
-        <v>910</v>
       </c>
       <c r="E375" s="1">
         <v>45717</v>
@@ -20082,7 +20190,7 @@
         <v>17500</v>
       </c>
       <c r="O375" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="P375">
         <v>3390</v>
@@ -20096,13 +20204,13 @@
     </row>
     <row r="376" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C376" t="s">
+        <v>904</v>
+      </c>
+      <c r="D376" t="s">
         <v>905</v>
-      </c>
-      <c r="D376" t="s">
-        <v>906</v>
       </c>
       <c r="E376" s="1">
         <v>45717</v>
@@ -20134,16 +20242,16 @@
     </row>
     <row r="377" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B377" s="5">
         <v>308000370887</v>
       </c>
       <c r="C377" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="D377" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E377" s="1">
         <v>45717</v>
@@ -20170,12 +20278,12 @@
         <v>36</v>
       </c>
       <c r="R377" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="378" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B378" s="5">
         <v>308190793917</v>
@@ -20216,13 +20324,13 @@
     </row>
     <row r="379" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
+        <v>914</v>
+      </c>
+      <c r="B379" s="5" t="s">
         <v>915</v>
       </c>
-      <c r="B379" s="5" t="s">
+      <c r="C379" t="s">
         <v>916</v>
-      </c>
-      <c r="C379" t="s">
-        <v>917</v>
       </c>
       <c r="D379" t="s">
         <v>307</v>
@@ -20257,13 +20365,13 @@
     </row>
     <row r="380" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B380" s="5">
         <v>308157299946</v>
       </c>
       <c r="C380" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D380" t="s">
         <v>113</v>
@@ -20298,13 +20406,13 @@
     </row>
     <row r="381" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B381" s="5">
         <v>308156995781</v>
       </c>
       <c r="C381" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D381" t="s">
         <v>113</v>
@@ -20339,13 +20447,13 @@
     </row>
     <row r="382" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B382" s="5">
         <v>308157141230</v>
       </c>
       <c r="C382" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D382" t="s">
         <v>736</v>
@@ -20375,21 +20483,21 @@
         <v>36</v>
       </c>
       <c r="R382" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="383" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B383" s="5">
         <v>308003956940</v>
       </c>
       <c r="C383" t="s">
+        <v>924</v>
+      </c>
+      <c r="D383" t="s">
         <v>925</v>
-      </c>
-      <c r="D383" t="s">
-        <v>926</v>
       </c>
       <c r="E383" s="1">
         <v>45748</v>
@@ -20421,7 +20529,7 @@
     </row>
     <row r="384" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B384" s="5">
         <v>310478039233</v>
@@ -20462,7 +20570,7 @@
     </row>
     <row r="385" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B385" s="5">
         <v>308156995787</v>
@@ -20489,7 +20597,7 @@
         <v>2578000</v>
       </c>
       <c r="O385" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="P385">
         <v>1489</v>
@@ -20503,13 +20611,13 @@
     </row>
     <row r="386" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B386" s="5">
         <v>308000379129</v>
       </c>
       <c r="C386" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D386" t="s">
         <v>599</v>
@@ -20544,13 +20652,13 @@
     </row>
     <row r="387" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B387" s="5">
         <v>308003949767</v>
       </c>
       <c r="C387" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D387" t="s">
         <v>352</v>
@@ -20585,16 +20693,16 @@
     </row>
     <row r="388" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B388" s="5">
         <v>308190610655</v>
       </c>
       <c r="C388" t="s">
+        <v>934</v>
+      </c>
+      <c r="D388" t="s">
         <v>935</v>
-      </c>
-      <c r="D388" t="s">
-        <v>936</v>
       </c>
       <c r="E388" s="1">
         <v>45748</v>
@@ -20621,21 +20729,21 @@
         <v>36</v>
       </c>
       <c r="R388" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="389" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B389" s="5">
         <v>308156240112</v>
       </c>
       <c r="C389" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D389" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E389" s="1">
         <v>45748</v>
@@ -20662,18 +20770,18 @@
         <v>36</v>
       </c>
       <c r="R389" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="390" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B390" s="5">
         <v>308156612832</v>
       </c>
       <c r="C390" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="D390" t="s">
         <v>188</v>
@@ -20708,13 +20816,13 @@
     </row>
     <row r="391" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B391" s="5">
         <v>308102573281</v>
       </c>
       <c r="C391" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D391" t="s">
         <v>298</v>
@@ -20735,7 +20843,7 @@
         <v>40000</v>
       </c>
       <c r="O391" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="P391">
         <v>3513</v>
@@ -20744,18 +20852,18 @@
         <v>36</v>
       </c>
       <c r="R391" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="392" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B392" s="5">
         <v>308102573281</v>
       </c>
       <c r="C392" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="D392" t="s">
         <v>298</v>
@@ -20776,7 +20884,7 @@
         <v>60000</v>
       </c>
       <c r="O392" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="P392">
         <v>3514</v>
@@ -20785,12 +20893,12 @@
         <v>36</v>
       </c>
       <c r="R392" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="393" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C393" t="s">
         <v>378</v>
@@ -20828,13 +20936,13 @@
     </row>
     <row r="394" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B394" s="5">
         <v>308084622566</v>
       </c>
       <c r="C394" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D394" t="s">
         <v>403</v>
@@ -20869,7 +20977,7 @@
     </row>
     <row r="395" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="C395" t="s">
         <v>551</v>
@@ -20907,13 +21015,13 @@
     </row>
     <row r="396" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
+        <v>948</v>
+      </c>
+      <c r="C396" t="s">
         <v>949</v>
       </c>
-      <c r="C396" t="s">
+      <c r="D396" t="s">
         <v>950</v>
-      </c>
-      <c r="D396" t="s">
-        <v>951</v>
       </c>
       <c r="E396" s="1">
         <v>45778</v>
@@ -20945,13 +21053,13 @@
     </row>
     <row r="397" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
+        <v>951</v>
+      </c>
+      <c r="C397" t="s">
         <v>952</v>
       </c>
-      <c r="C397" t="s">
-        <v>953</v>
-      </c>
       <c r="D397" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E397" s="1">
         <v>45778</v>
@@ -20983,16 +21091,16 @@
     </row>
     <row r="398" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B398" s="5">
         <v>307838833884</v>
       </c>
       <c r="C398" t="s">
+        <v>954</v>
+      </c>
+      <c r="D398" t="s">
         <v>955</v>
-      </c>
-      <c r="D398" t="s">
-        <v>956</v>
       </c>
       <c r="E398" s="1">
         <v>45778</v>
@@ -21024,13 +21132,13 @@
     </row>
     <row r="399" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
+        <v>956</v>
+      </c>
+      <c r="C399" t="s">
         <v>957</v>
       </c>
-      <c r="C399" t="s">
-        <v>958</v>
-      </c>
       <c r="D399" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E399" s="1">
         <v>45778</v>
@@ -21062,7 +21170,7 @@
     </row>
     <row r="400" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B400" s="5">
         <v>308157293777</v>
@@ -21103,13 +21211,13 @@
     </row>
     <row r="401" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
+        <v>959</v>
+      </c>
+      <c r="C401" t="s">
         <v>960</v>
       </c>
-      <c r="C401" t="s">
+      <c r="D401" t="s">
         <v>961</v>
-      </c>
-      <c r="D401" t="s">
-        <v>962</v>
       </c>
       <c r="E401" s="1">
         <v>45778</v>
@@ -21136,18 +21244,18 @@
         <v>36</v>
       </c>
       <c r="R401" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="402" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B402" s="5">
         <v>308157141215</v>
       </c>
       <c r="C402" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="D402" t="s">
         <v>266</v>
@@ -21168,7 +21276,7 @@
         <v>1460000</v>
       </c>
       <c r="O402" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="P402">
         <v>3507</v>
@@ -21182,10 +21290,10 @@
     </row>
     <row r="403" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
+        <v>964</v>
+      </c>
+      <c r="C403" t="s">
         <v>965</v>
-      </c>
-      <c r="C403" t="s">
-        <v>966</v>
       </c>
       <c r="D403" t="s">
         <v>188</v>
@@ -21220,16 +21328,16 @@
     </row>
     <row r="404" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B404" s="5">
         <v>308084622544</v>
       </c>
       <c r="C404" t="s">
+        <v>967</v>
+      </c>
+      <c r="D404" t="s">
         <v>968</v>
-      </c>
-      <c r="D404" t="s">
-        <v>969</v>
       </c>
       <c r="E404" s="1">
         <v>45809</v>
@@ -21256,21 +21364,21 @@
         <v>36</v>
       </c>
       <c r="R404" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="405" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B405" s="5">
         <v>308084622544</v>
       </c>
       <c r="C405" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D405" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E405" s="1">
         <v>45809</v>
@@ -21297,18 +21405,18 @@
         <v>36</v>
       </c>
       <c r="R405" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="406" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B406" s="5">
         <v>308190793924</v>
       </c>
       <c r="C406" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="D406" t="s">
         <v>132</v>
@@ -21343,13 +21451,13 @@
     </row>
     <row r="407" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B407" s="5">
         <v>308190793924</v>
       </c>
       <c r="C407" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D407" t="s">
         <v>132</v>
@@ -21384,16 +21492,16 @@
     </row>
     <row r="408" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
+        <v>975</v>
+      </c>
+      <c r="B408" s="5" t="s">
         <v>976</v>
       </c>
-      <c r="B408" s="5" t="s">
+      <c r="C408" t="s">
         <v>977</v>
       </c>
-      <c r="C408" t="s">
+      <c r="D408" t="s">
         <v>978</v>
-      </c>
-      <c r="D408" t="s">
-        <v>979</v>
       </c>
       <c r="E408" s="1">
         <v>45809</v>
@@ -21411,7 +21519,7 @@
         <v>632500</v>
       </c>
       <c r="O408" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P408">
         <v>3568</v>
@@ -21425,16 +21533,16 @@
     </row>
     <row r="409" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
+        <v>980</v>
+      </c>
+      <c r="B409" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="C409" t="s">
         <v>981</v>
       </c>
-      <c r="B409" s="5" t="s">
-        <v>977</v>
-      </c>
-      <c r="C409" t="s">
-        <v>982</v>
-      </c>
       <c r="D409" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E409" s="1">
         <v>45809</v>
@@ -21452,7 +21560,7 @@
         <v>517500</v>
       </c>
       <c r="O409" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P409">
         <v>3567</v>
@@ -21466,10 +21574,10 @@
     </row>
     <row r="410" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
+        <v>982</v>
+      </c>
+      <c r="C410" t="s">
         <v>983</v>
-      </c>
-      <c r="C410" t="s">
-        <v>984</v>
       </c>
       <c r="D410" t="s">
         <v>113</v>
@@ -21504,13 +21612,13 @@
     </row>
     <row r="411" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B411" s="5">
         <v>308000371934</v>
       </c>
       <c r="C411" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="D411" t="s">
         <v>153</v>
@@ -21545,7 +21653,7 @@
     </row>
     <row r="412" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="C412" t="s">
         <v>185</v>
@@ -21583,16 +21691,16 @@
     </row>
     <row r="413" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B413" s="5">
         <v>308084619450</v>
       </c>
       <c r="C413" t="s">
+        <v>988</v>
+      </c>
+      <c r="D413" t="s">
         <v>989</v>
-      </c>
-      <c r="D413" t="s">
-        <v>990</v>
       </c>
       <c r="E413" s="1">
         <v>45809</v>
@@ -21610,7 +21718,7 @@
         <v>107000</v>
       </c>
       <c r="O413" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P413">
         <v>3575</v>
@@ -21619,12 +21727,12 @@
         <v>36</v>
       </c>
       <c r="R413" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="414" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C414" t="s">
         <v>91</v>
@@ -21662,16 +21770,16 @@
     </row>
     <row r="415" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B415" s="5">
         <v>308102573244</v>
       </c>
       <c r="C415" t="s">
+        <v>992</v>
+      </c>
+      <c r="D415" t="s">
         <v>993</v>
-      </c>
-      <c r="D415" t="s">
-        <v>994</v>
       </c>
       <c r="E415" s="1">
         <v>45809</v>
@@ -21698,12 +21806,12 @@
         <v>36</v>
       </c>
       <c r="R415" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="416" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B416" s="5">
         <v>308152808656</v>
@@ -21744,16 +21852,16 @@
     </row>
     <row r="417" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B417" s="5">
         <v>308073980132</v>
       </c>
       <c r="C417" t="s">
+        <v>996</v>
+      </c>
+      <c r="D417" t="s">
         <v>997</v>
-      </c>
-      <c r="D417" t="s">
-        <v>998</v>
       </c>
       <c r="E417" s="1">
         <v>45809</v>
@@ -21780,21 +21888,21 @@
         <v>36</v>
       </c>
       <c r="R417" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="418" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B418" s="5">
         <v>308073980132</v>
       </c>
       <c r="C418" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D418" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E418" s="1">
         <v>45809</v>
@@ -21821,18 +21929,18 @@
         <v>36</v>
       </c>
       <c r="R418" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="419" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C419" t="s">
         <v>1001</v>
       </c>
-      <c r="C419" t="s">
+      <c r="D419" t="s">
         <v>1002</v>
-      </c>
-      <c r="D419" t="s">
-        <v>1003</v>
       </c>
       <c r="E419" s="1">
         <v>45839</v>
@@ -21864,10 +21972,10 @@
     </row>
     <row r="420" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C420" t="s">
         <v>1004</v>
-      </c>
-      <c r="C420" t="s">
-        <v>1005</v>
       </c>
       <c r="D420" t="s">
         <v>113</v>
@@ -21902,10 +22010,10 @@
     </row>
     <row r="421" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C421" t="s">
         <v>1006</v>
-      </c>
-      <c r="C421" t="s">
-        <v>1007</v>
       </c>
       <c r="D421" t="s">
         <v>113</v>
@@ -21940,16 +22048,16 @@
     </row>
     <row r="422" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B422" s="5" t="s">
         <v>1008</v>
       </c>
-      <c r="B422" s="5" t="s">
+      <c r="C422" t="s">
         <v>1009</v>
       </c>
-      <c r="C422" t="s">
-        <v>1010</v>
-      </c>
       <c r="D422" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E422" s="1">
         <v>45839</v>
@@ -21967,7 +22075,7 @@
         <v>44701.027329999997</v>
       </c>
       <c r="O422" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="P422">
         <v>3601</v>
@@ -21981,16 +22089,16 @@
     </row>
     <row r="423" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B423" s="5" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C423" t="s">
         <v>1012</v>
       </c>
-      <c r="B423" s="5" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C423" t="s">
-        <v>1013</v>
-      </c>
       <c r="D423" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E423" s="1">
         <v>45839</v>
@@ -22008,7 +22116,7 @@
         <v>27938.142080000001</v>
       </c>
       <c r="O423" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="P423">
         <v>3602</v>
@@ -22022,16 +22130,16 @@
     </row>
     <row r="424" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B424" s="5">
         <v>308152808637</v>
       </c>
       <c r="C424" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D424" t="s">
         <v>1015</v>
-      </c>
-      <c r="D424" t="s">
-        <v>1016</v>
       </c>
       <c r="E424" s="1">
         <v>45809</v>
@@ -22049,7 +22157,7 @@
         <v>319000</v>
       </c>
       <c r="O424" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="P424">
         <v>3604</v>
@@ -22058,21 +22166,21 @@
         <v>36</v>
       </c>
       <c r="R424" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="425" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B425" s="5">
         <v>308152808637</v>
       </c>
       <c r="C425" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D425" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E425" s="1">
         <v>45809</v>
@@ -22090,7 +22198,7 @@
         <v>518000</v>
       </c>
       <c r="O425" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="P425">
         <v>3605</v>
@@ -22099,12 +22207,12 @@
         <v>36</v>
       </c>
       <c r="R425" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="426" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C426" t="s">
         <v>355</v>
@@ -22142,7 +22250,7 @@
     </row>
     <row r="427" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="C427" t="s">
         <v>397</v>
@@ -22180,13 +22288,13 @@
     </row>
     <row r="428" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C428" t="s">
         <v>1022</v>
       </c>
-      <c r="C428" t="s">
-        <v>1023</v>
-      </c>
       <c r="D428" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E428" s="1">
         <v>45839</v>
@@ -22218,10 +22326,10 @@
     </row>
     <row r="429" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C429" t="s">
         <v>1024</v>
-      </c>
-      <c r="C429" t="s">
-        <v>1025</v>
       </c>
       <c r="D429" t="s">
         <v>102</v>
@@ -22256,7 +22364,7 @@
     </row>
     <row r="430" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="C430" t="s">
         <v>341</v>
@@ -22294,7 +22402,7 @@
     </row>
     <row r="431" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="C431" t="s">
         <v>349</v>
@@ -22332,7 +22440,7 @@
     </row>
     <row r="432" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="C432" t="s">
         <v>714</v>
@@ -22370,7 +22478,7 @@
     </row>
     <row r="433" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="C433" t="s">
         <v>717</v>
@@ -22408,7 +22516,7 @@
     </row>
     <row r="434" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="C434" t="s">
         <v>639</v>
@@ -22446,7 +22554,7 @@
     </row>
     <row r="435" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="C435" t="s">
         <v>417</v>
@@ -22484,13 +22592,13 @@
     </row>
     <row r="436" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C436" t="s">
         <v>1032</v>
       </c>
-      <c r="C436" t="s">
+      <c r="D436" t="s">
         <v>1033</v>
-      </c>
-      <c r="D436" t="s">
-        <v>1034</v>
       </c>
       <c r="E436" s="1">
         <v>45809</v>
@@ -22522,13 +22630,13 @@
     </row>
     <row r="437" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C437" t="s">
         <v>1035</v>
       </c>
-      <c r="C437" t="s">
-        <v>1036</v>
-      </c>
       <c r="D437" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E437" s="1">
         <v>45809</v>
@@ -22560,16 +22668,16 @@
     </row>
     <row r="438" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B438" s="5">
         <v>308156775617</v>
       </c>
       <c r="C438" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D438" t="s">
         <v>1038</v>
-      </c>
-      <c r="D438" t="s">
-        <v>1039</v>
       </c>
       <c r="E438" s="1">
         <v>45839</v>
@@ -22596,21 +22704,21 @@
         <v>36</v>
       </c>
       <c r="R438" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="439" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B439" s="5">
         <v>308156775617</v>
       </c>
       <c r="C439" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="D439" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E439" s="1">
         <v>45839</v>
@@ -22637,15 +22745,15 @@
         <v>36</v>
       </c>
       <c r="R439" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="440" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C440" t="s">
         <v>1042</v>
-      </c>
-      <c r="C440" t="s">
-        <v>1043</v>
       </c>
       <c r="D440" t="s">
         <v>188</v>
@@ -22680,16 +22788,16 @@
     </row>
     <row r="441" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B441" s="5">
         <v>308102571229</v>
       </c>
       <c r="C441" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D441" t="s">
         <v>1045</v>
-      </c>
-      <c r="D441" t="s">
-        <v>1046</v>
       </c>
       <c r="E441" s="1">
         <v>45839</v>
@@ -22716,21 +22824,21 @@
         <v>36</v>
       </c>
       <c r="R441" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="442" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B442" s="5">
         <v>308102571229</v>
       </c>
       <c r="C442" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="D442" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E442" s="1">
         <v>45839</v>
@@ -22757,18 +22865,18 @@
         <v>36</v>
       </c>
       <c r="R442" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="443" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B443" s="5">
         <v>308156239088</v>
       </c>
       <c r="C443" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="D443" t="s">
         <v>113</v>
@@ -22803,13 +22911,13 @@
     </row>
     <row r="444" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B444" s="5">
         <v>308152804599</v>
       </c>
       <c r="C444" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="D444" t="s">
         <v>113</v>
@@ -22844,13 +22952,13 @@
     </row>
     <row r="445" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B445" s="5">
         <v>308000380092</v>
       </c>
       <c r="C445" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="D445" t="s">
         <v>132</v>
@@ -22871,7 +22979,7 @@
         <v>40000</v>
       </c>
       <c r="O445" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="P445">
         <v>3632</v>
@@ -22885,13 +22993,13 @@
     </row>
     <row r="446" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B446" s="5">
         <v>308000380092</v>
       </c>
       <c r="C446" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="D446" t="s">
         <v>132</v>
@@ -22912,7 +23020,7 @@
         <v>32000</v>
       </c>
       <c r="O446" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="P446">
         <v>3633</v>
@@ -22926,7 +23034,7 @@
     </row>
     <row r="447" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B447" s="5">
         <v>308102573247</v>
@@ -22967,7 +23075,7 @@
     </row>
     <row r="448" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B448" s="5">
         <v>308102573247</v>
@@ -23008,16 +23116,16 @@
     </row>
     <row r="449" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B449" s="5">
         <v>308073980110</v>
       </c>
       <c r="C449" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D449" t="s">
         <v>1061</v>
-      </c>
-      <c r="D449" t="s">
-        <v>1062</v>
       </c>
       <c r="E449" s="1">
         <v>45839</v>
@@ -23044,21 +23152,21 @@
         <v>36</v>
       </c>
       <c r="R449" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="450" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B450" s="5">
         <v>308073980110</v>
       </c>
       <c r="C450" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="D450" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E450" s="1">
         <v>45839</v>
@@ -23085,12 +23193,12 @@
         <v>36</v>
       </c>
       <c r="R450" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="451" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="C451" t="s">
         <v>397</v>
@@ -23128,7 +23236,7 @@
     </row>
     <row r="452" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="C452" t="s">
         <v>341</v>
@@ -23166,16 +23274,16 @@
     </row>
     <row r="453" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B453" s="5">
         <v>308102577375</v>
       </c>
       <c r="C453" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D453" t="s">
         <v>1068</v>
-      </c>
-      <c r="D453" t="s">
-        <v>1069</v>
       </c>
       <c r="E453" s="1">
         <v>45839</v>
@@ -23202,21 +23310,21 @@
         <v>36</v>
       </c>
       <c r="R453" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="454" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B454" s="5">
         <v>308102577375</v>
       </c>
       <c r="C454" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="D454" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="E454" s="1">
         <v>45839</v>
@@ -23243,21 +23351,21 @@
         <v>36</v>
       </c>
       <c r="R454" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="455" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B455" s="5">
         <v>308190618865</v>
       </c>
       <c r="C455" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D455" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E455" s="1">
         <v>45839</v>
@@ -23289,7 +23397,7 @@
     </row>
     <row r="456" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B456" s="5">
         <v>308156775611</v>
@@ -23330,13 +23438,13 @@
     </row>
     <row r="457" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B457" s="5">
         <v>308190615753</v>
       </c>
       <c r="C457" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D457" t="s">
         <v>188</v>
@@ -23371,7 +23479,7 @@
     </row>
     <row r="458" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B458" s="5">
         <v>308157141222</v>
@@ -23412,7 +23520,7 @@
     </row>
     <row r="459" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C459" t="s">
         <v>66</v>
@@ -23450,10 +23558,10 @@
     </row>
     <row r="460" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C460" t="s">
         <v>1078</v>
-      </c>
-      <c r="C460" t="s">
-        <v>1079</v>
       </c>
       <c r="D460" t="s">
         <v>113</v>
@@ -23488,7 +23596,7 @@
     </row>
     <row r="461" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B461" s="5">
         <v>308156774612</v>
@@ -23529,13 +23637,13 @@
     </row>
     <row r="462" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C462" t="s">
         <v>1081</v>
       </c>
-      <c r="C462" t="s">
-        <v>1082</v>
-      </c>
       <c r="D462" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E462" s="1">
         <v>45870</v>
@@ -23553,7 +23661,7 @@
         <v>25000</v>
       </c>
       <c r="O462" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="P462">
         <v>3662</v>
@@ -23567,13 +23675,13 @@
     </row>
     <row r="463" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C463" t="s">
         <v>1084</v>
       </c>
-      <c r="C463" t="s">
+      <c r="D463" t="s">
         <v>1085</v>
-      </c>
-      <c r="D463" t="s">
-        <v>1086</v>
       </c>
       <c r="E463" s="1">
         <v>45870</v>
@@ -23605,10 +23713,10 @@
     </row>
     <row r="464" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C464" t="s">
         <v>1087</v>
-      </c>
-      <c r="C464" t="s">
-        <v>1088</v>
       </c>
       <c r="D464" t="s">
         <v>140</v>
@@ -23643,10 +23751,10 @@
     </row>
     <row r="465" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C465" t="s">
         <v>1089</v>
-      </c>
-      <c r="C465" t="s">
-        <v>1090</v>
       </c>
       <c r="D465" t="s">
         <v>165</v>
@@ -23681,7 +23789,7 @@
     </row>
     <row r="466" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C466" t="s">
         <v>164</v>
@@ -23719,16 +23827,16 @@
     </row>
     <row r="467" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B467" s="5">
         <v>308084622538</v>
       </c>
       <c r="C467" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D467" t="s">
         <v>1093</v>
-      </c>
-      <c r="D467" t="s">
-        <v>1094</v>
       </c>
       <c r="E467" s="1">
         <v>45870</v>
@@ -23755,21 +23863,21 @@
         <v>36</v>
       </c>
       <c r="R467" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="468" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B468" s="5">
         <v>308084622538</v>
       </c>
       <c r="C468" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="D468" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="E468" s="1">
         <v>45870</v>
@@ -23796,21 +23904,21 @@
         <v>36</v>
       </c>
       <c r="R468" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="469" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B469" s="5">
         <v>308156452068</v>
       </c>
       <c r="C469" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D469" t="s">
         <v>1098</v>
-      </c>
-      <c r="D469" t="s">
-        <v>1099</v>
       </c>
       <c r="E469" s="1">
         <v>45870</v>
@@ -23837,21 +23945,21 @@
         <v>36</v>
       </c>
       <c r="R469" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="470" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B470" s="5">
         <v>308156452068</v>
       </c>
       <c r="C470" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D470" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="E470" s="1">
         <v>45870</v>
@@ -23878,21 +23986,21 @@
         <v>36</v>
       </c>
       <c r="R470" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="471" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B471" s="5">
         <v>308084622530</v>
       </c>
       <c r="C471" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D471" t="s">
         <v>1103</v>
-      </c>
-      <c r="D471" t="s">
-        <v>1104</v>
       </c>
       <c r="E471" s="1">
         <v>45870</v>
@@ -23910,7 +24018,7 @@
         <v>2964835</v>
       </c>
       <c r="O471" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="P471">
         <v>3678</v>
@@ -23919,21 +24027,21 @@
         <v>36</v>
       </c>
       <c r="R471" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="472" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B472" s="5">
         <v>308084622530</v>
       </c>
       <c r="C472" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D472" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="E472" s="1">
         <v>45870</v>
@@ -23951,7 +24059,7 @@
         <v>7188600</v>
       </c>
       <c r="O472" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="P472">
         <v>3679</v>
@@ -23960,12 +24068,12 @@
         <v>36</v>
       </c>
       <c r="R472" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="473" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="C473" t="s">
         <v>355</v>
@@ -24003,10 +24111,10 @@
     </row>
     <row r="474" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C474" t="s">
         <v>1109</v>
-      </c>
-      <c r="C474" t="s">
-        <v>1110</v>
       </c>
       <c r="D474" t="s">
         <v>113</v>
@@ -24041,16 +24149,16 @@
     </row>
     <row r="475" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B475" s="5">
         <v>308156612846</v>
       </c>
       <c r="C475" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D475" t="s">
         <v>1112</v>
-      </c>
-      <c r="D475" t="s">
-        <v>1113</v>
       </c>
       <c r="E475" s="1">
         <v>45901</v>
@@ -24077,21 +24185,21 @@
         <v>36</v>
       </c>
       <c r="R475" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="476" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B476" s="5">
         <v>308156612846</v>
       </c>
       <c r="C476" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D476" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E476" s="1">
         <v>45901</v>
@@ -24118,15 +24226,15 @@
         <v>36</v>
       </c>
       <c r="R476" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="477" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C477" t="s">
         <v>1116</v>
-      </c>
-      <c r="C477" t="s">
-        <v>1117</v>
       </c>
       <c r="D477" t="s">
         <v>132</v>
@@ -24161,13 +24269,13 @@
     </row>
     <row r="478" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C478" t="s">
         <v>1118</v>
       </c>
-      <c r="C478" t="s">
+      <c r="D478" t="s">
         <v>1119</v>
-      </c>
-      <c r="D478" t="s">
-        <v>1120</v>
       </c>
       <c r="E478" s="1">
         <v>45901</v>
@@ -24199,13 +24307,13 @@
     </row>
     <row r="479" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C479" t="s">
         <v>1121</v>
       </c>
-      <c r="C479" t="s">
+      <c r="D479" t="s">
         <v>1122</v>
-      </c>
-      <c r="D479" t="s">
-        <v>1123</v>
       </c>
       <c r="E479" s="1">
         <v>45901</v>
@@ -24237,16 +24345,16 @@
     </row>
     <row r="480" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B480" s="5">
         <v>308102577391</v>
       </c>
       <c r="C480" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D480" t="s">
         <v>1125</v>
-      </c>
-      <c r="D480" t="s">
-        <v>1126</v>
       </c>
       <c r="E480" s="1">
         <v>45901</v>
@@ -24273,12 +24381,12 @@
         <v>36</v>
       </c>
       <c r="R480" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="481" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B481" s="5">
         <v>310438207719</v>
@@ -24319,13 +24427,13 @@
     </row>
     <row r="482" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B482" s="5">
         <v>313139406062</v>
       </c>
       <c r="C482" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="D482" t="s">
         <v>113</v>
@@ -24360,13 +24468,13 @@
     </row>
     <row r="483" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C483" t="s">
         <v>1130</v>
       </c>
-      <c r="C483" t="s">
-        <v>1131</v>
-      </c>
       <c r="D483" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E483" s="1">
         <v>45901</v>
@@ -24398,16 +24506,16 @@
     </row>
     <row r="484" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B484" s="5">
         <v>308156621033</v>
       </c>
       <c r="C484" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D484" t="s">
         <v>1133</v>
-      </c>
-      <c r="D484" t="s">
-        <v>1134</v>
       </c>
       <c r="E484" s="1">
         <v>45901</v>
@@ -24425,7 +24533,7 @@
         <v>17261.50417</v>
       </c>
       <c r="O484" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P484">
         <v>3703</v>
@@ -24434,21 +24542,21 @@
         <v>36</v>
       </c>
       <c r="R484" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="485" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B485" s="5">
         <v>308156621033</v>
       </c>
       <c r="C485" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D485" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="E485" s="1">
         <v>45901</v>
@@ -24466,7 +24574,7 @@
         <v>23015</v>
       </c>
       <c r="O485" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P485">
         <v>3704</v>
@@ -24475,18 +24583,18 @@
         <v>36</v>
       </c>
       <c r="R485" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="486" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B486" s="5">
         <v>307840780519</v>
       </c>
       <c r="C486" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D486" t="s">
         <v>237</v>
@@ -24521,7 +24629,7 @@
     </row>
     <row r="487" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C487" t="s">
         <v>178</v>
@@ -24559,16 +24667,16 @@
     </row>
     <row r="488" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B488" s="5">
         <v>307810410709</v>
       </c>
       <c r="C488" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D488" t="s">
         <v>1142</v>
-      </c>
-      <c r="D488" t="s">
-        <v>1143</v>
       </c>
       <c r="E488" s="1">
         <v>45901</v>
@@ -24595,21 +24703,21 @@
         <v>36</v>
       </c>
       <c r="R488" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="489" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B489" s="5">
         <v>307810410709</v>
       </c>
       <c r="C489" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D489" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="E489" s="1">
         <v>45901</v>
@@ -24636,21 +24744,21 @@
         <v>36</v>
       </c>
       <c r="R489" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="490" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B490" s="5">
         <v>308000371953</v>
       </c>
       <c r="C490" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D490" t="s">
         <v>1147</v>
-      </c>
-      <c r="D490" t="s">
-        <v>1148</v>
       </c>
       <c r="E490" s="1">
         <v>45931</v>
@@ -24677,21 +24785,21 @@
         <v>36</v>
       </c>
       <c r="R490" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="491" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B491" s="5">
         <v>308000371953</v>
       </c>
       <c r="C491" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D491" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="E491" s="1">
         <v>45931</v>
@@ -24718,15 +24826,15 @@
         <v>36</v>
       </c>
       <c r="R491" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="492" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C492" t="s">
         <v>1151</v>
-      </c>
-      <c r="C492" t="s">
-        <v>1152</v>
       </c>
       <c r="D492" t="s">
         <v>287</v>
@@ -24761,16 +24869,16 @@
     </row>
     <row r="493" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B493" s="5">
         <v>308073981154</v>
       </c>
       <c r="C493" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D493" t="s">
         <v>1154</v>
-      </c>
-      <c r="D493" t="s">
-        <v>1155</v>
       </c>
       <c r="E493" s="1">
         <v>45931</v>
@@ -24788,7 +24896,7 @@
         <v>138263.4283</v>
       </c>
       <c r="O493" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="P493">
         <v>3723</v>
@@ -24797,21 +24905,21 @@
         <v>36</v>
       </c>
       <c r="R493" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="494" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B494" s="5">
         <v>308073981154</v>
       </c>
       <c r="C494" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D494" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="E494" s="1">
         <v>45931</v>
@@ -24829,7 +24937,7 @@
         <v>186593</v>
       </c>
       <c r="O494" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="P494">
         <v>3724</v>
@@ -24838,21 +24946,21 @@
         <v>36</v>
       </c>
       <c r="R494" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="495" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B495" s="5">
         <v>307916948674</v>
       </c>
       <c r="C495" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D495" t="s">
         <v>1160</v>
-      </c>
-      <c r="D495" t="s">
-        <v>1161</v>
       </c>
       <c r="E495" s="1">
         <v>45901</v>
@@ -24870,7 +24978,7 @@
         <v>195856.66829999999</v>
       </c>
       <c r="O495" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="P495">
         <v>3725</v>
@@ -24879,18 +24987,18 @@
         <v>36</v>
       </c>
       <c r="R495" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="496" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B496" s="5">
         <v>322798526657</v>
       </c>
       <c r="C496" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D496" t="s">
         <v>431</v>
@@ -24925,10 +25033,10 @@
     </row>
     <row r="497" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C497" t="s">
         <v>1164</v>
-      </c>
-      <c r="C497" t="s">
-        <v>1165</v>
       </c>
       <c r="D497" t="s">
         <v>307</v>
@@ -24963,7 +25071,7 @@
     </row>
     <row r="498" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="C498" t="s">
         <v>29</v>
@@ -25001,7 +25109,7 @@
     </row>
     <row r="499" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C499" t="s">
         <v>515</v>
@@ -25039,13 +25147,13 @@
     </row>
     <row r="500" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C500" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D500" t="s">
         <v>1033</v>
-      </c>
-      <c r="D500" t="s">
-        <v>1034</v>
       </c>
       <c r="E500" s="1">
         <v>45901</v>
@@ -25077,13 +25185,13 @@
     </row>
     <row r="501" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C501" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D501" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E501" s="1">
         <v>45901</v>
@@ -25115,7 +25223,7 @@
     </row>
     <row r="502" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C502" t="s">
         <v>639</v>
@@ -25153,7 +25261,7 @@
     </row>
     <row r="503" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C503" t="s">
         <v>417</v>
@@ -25191,7 +25299,7 @@
     </row>
     <row r="504" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="C504" t="s">
         <v>611</v>
@@ -25229,16 +25337,16 @@
     </row>
     <row r="505" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B505" s="5">
         <v>308156610769</v>
       </c>
       <c r="C505" t="s">
+        <v>1173</v>
+      </c>
+      <c r="D505" t="s">
         <v>1174</v>
-      </c>
-      <c r="D505" t="s">
-        <v>1175</v>
       </c>
       <c r="E505" s="1">
         <v>45901</v>
@@ -25265,18 +25373,18 @@
         <v>36</v>
       </c>
       <c r="R505" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="506" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C506" t="s">
         <v>1176</v>
       </c>
-      <c r="C506" t="s">
-        <v>1177</v>
-      </c>
       <c r="D506" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E506" s="1">
         <v>45901</v>
@@ -25303,21 +25411,21 @@
         <v>36</v>
       </c>
       <c r="R506" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="507" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B507" s="5">
         <v>307840817384</v>
       </c>
       <c r="C507" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D507" t="s">
         <v>1179</v>
-      </c>
-      <c r="D507" t="s">
-        <v>1180</v>
       </c>
       <c r="E507" s="1">
         <v>45931</v>
@@ -25344,21 +25452,21 @@
         <v>36</v>
       </c>
       <c r="R507" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="508" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B508" s="5">
         <v>307840817384</v>
       </c>
       <c r="C508" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D508" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E508" s="1">
         <v>45931</v>
@@ -25385,21 +25493,21 @@
         <v>36</v>
       </c>
       <c r="R508" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="509" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="B509" s="5">
         <v>307840817384</v>
       </c>
       <c r="C509" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="D509" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E509" s="1">
         <v>45931</v>
@@ -25426,12 +25534,12 @@
         <v>36</v>
       </c>
       <c r="R509" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="510" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C510" t="s">
         <v>575</v>
@@ -25469,16 +25577,16 @@
     </row>
     <row r="511" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B511" s="5">
         <v>308102571238</v>
       </c>
       <c r="C511" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D511" t="s">
         <v>1187</v>
-      </c>
-      <c r="D511" t="s">
-        <v>1188</v>
       </c>
       <c r="E511" s="1">
         <v>45931</v>
@@ -25505,21 +25613,21 @@
         <v>36</v>
       </c>
       <c r="R511" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="512" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B512" s="5">
         <v>308156992702</v>
       </c>
       <c r="C512" t="s">
+        <v>1189</v>
+      </c>
+      <c r="D512" t="s">
         <v>1190</v>
-      </c>
-      <c r="D512" t="s">
-        <v>1191</v>
       </c>
       <c r="E512" s="1">
         <v>45931</v>
@@ -25546,21 +25654,21 @@
         <v>36</v>
       </c>
       <c r="R512" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="513" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B513" s="5">
         <v>308156992702</v>
       </c>
       <c r="C513" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="D513" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="E513" s="1">
         <v>45931</v>
@@ -25587,18 +25695,18 @@
         <v>36</v>
       </c>
       <c r="R513" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="514" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B514" s="5">
         <v>308152808659</v>
       </c>
       <c r="C514" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D514" t="s">
         <v>140</v>
@@ -25628,12 +25736,12 @@
         <v>36</v>
       </c>
       <c r="R514" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="515" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C515" t="s">
         <v>621</v>
@@ -25671,13 +25779,13 @@
     </row>
     <row r="516" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C516" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D516" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E516" s="1">
         <v>45931</v>
@@ -25695,7 +25803,7 @@
         <v>48000</v>
       </c>
       <c r="O516" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="P516">
         <v>3463</v>
@@ -25709,10 +25817,10 @@
     </row>
     <row r="517" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C517" t="s">
         <v>1198</v>
-      </c>
-      <c r="C517" t="s">
-        <v>1199</v>
       </c>
       <c r="D517" t="s">
         <v>544</v>
@@ -25733,7 +25841,7 @@
         <v>175000</v>
       </c>
       <c r="O517" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="P517">
         <v>3748</v>
@@ -25747,7 +25855,7 @@
     </row>
     <row r="518" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C518" t="s">
         <v>621</v>
@@ -25779,10 +25887,10 @@
     </row>
     <row r="519" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C519" t="s">
         <v>1202</v>
-      </c>
-      <c r="C519" t="s">
-        <v>1203</v>
       </c>
       <c r="D519" t="s">
         <v>113</v>
@@ -25817,13 +25925,13 @@
     </row>
     <row r="520" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B520" s="5">
         <v>308152812741</v>
       </c>
       <c r="C520" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D520" t="s">
         <v>298</v>
@@ -25858,13 +25966,13 @@
     </row>
     <row r="521" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B521" s="5">
         <v>308152812741</v>
       </c>
       <c r="C521" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D521" t="s">
         <v>298</v>
@@ -25899,13 +26007,13 @@
     </row>
     <row r="522" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B522" s="5">
         <v>308152812741</v>
       </c>
       <c r="C522" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D522" t="s">
         <v>298</v>
@@ -25940,13 +26048,13 @@
     </row>
     <row r="523" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B523" s="5">
         <v>308152812741</v>
       </c>
       <c r="C523" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="D523" t="s">
         <v>298</v>
@@ -25981,7 +26089,7 @@
     </row>
     <row r="524" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="C524" t="s">
         <v>112</v>
@@ -26005,7 +26113,7 @@
         <v>31920</v>
       </c>
       <c r="O524" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="P524">
         <v>2954</v>
@@ -26019,16 +26127,16 @@
     </row>
     <row r="525" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B525" s="5">
         <v>308102567106</v>
       </c>
       <c r="C525" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D525" t="s">
         <v>1214</v>
-      </c>
-      <c r="D525" t="s">
-        <v>1215</v>
       </c>
       <c r="E525" s="1">
         <v>45931</v>
@@ -26055,21 +26163,21 @@
         <v>36</v>
       </c>
       <c r="R525" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="526" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B526" s="5">
         <v>308102567106</v>
       </c>
       <c r="C526" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D526" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="E526" s="1">
         <v>45931</v>
@@ -26096,21 +26204,21 @@
         <v>36</v>
       </c>
       <c r="R526" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="527" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B527" s="5">
         <v>307841448132</v>
       </c>
       <c r="C527" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D527" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E527" s="1">
         <v>45931</v>
@@ -26142,7 +26250,7 @@
     </row>
     <row r="528" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="C528" t="s">
         <v>149</v>
@@ -26166,7 +26274,7 @@
         <v>49500</v>
       </c>
       <c r="O528" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="P528">
         <v>524</v>
@@ -26180,10 +26288,10 @@
     </row>
     <row r="529" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C529" t="s">
         <v>1222</v>
-      </c>
-      <c r="C529" t="s">
-        <v>1223</v>
       </c>
       <c r="D529" t="s">
         <v>123</v>
@@ -26204,7 +26312,7 @@
         <v>20000</v>
       </c>
       <c r="O529" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="P529">
         <v>3785</v>
@@ -26218,7 +26326,7 @@
     </row>
     <row r="530" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C530" t="s">
         <v>397</v>
@@ -26256,7 +26364,7 @@
     </row>
     <row r="531" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C531" t="s">
         <v>178</v>
@@ -26294,16 +26402,16 @@
     </row>
     <row r="532" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="B532" s="5" t="s">
+        <v>976</v>
+      </c>
+      <c r="C532" t="s">
         <v>977</v>
       </c>
-      <c r="C532" t="s">
+      <c r="D532" t="s">
         <v>978</v>
-      </c>
-      <c r="D532" t="s">
-        <v>979</v>
       </c>
       <c r="E532" s="1">
         <v>45962</v>
@@ -26321,7 +26429,7 @@
         <v>-230000</v>
       </c>
       <c r="O532" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P532">
         <v>3568</v>
@@ -26335,16 +26443,16 @@
     </row>
     <row r="533" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="B533" s="5" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="C533" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D533" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E533" s="1">
         <v>45962</v>
@@ -26362,7 +26470,7 @@
         <v>-230000</v>
       </c>
       <c r="O533" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="P533">
         <v>3567</v>
@@ -26376,10 +26484,10 @@
     </row>
     <row r="534" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C534" t="s">
         <v>1229</v>
-      </c>
-      <c r="C534" t="s">
-        <v>1230</v>
       </c>
       <c r="D534" t="s">
         <v>237</v>
@@ -26414,13 +26522,13 @@
     </row>
     <row r="535" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C535" t="s">
         <v>1231</v>
       </c>
-      <c r="C535" t="s">
+      <c r="D535" t="s">
         <v>1232</v>
-      </c>
-      <c r="D535" t="s">
-        <v>1233</v>
       </c>
       <c r="E535" s="1">
         <v>45962</v>
@@ -26447,18 +26555,18 @@
         <v>36</v>
       </c>
       <c r="R535" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="536" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C536" t="s">
         <v>1234</v>
       </c>
-      <c r="C536" t="s">
-        <v>1235</v>
-      </c>
       <c r="D536" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="E536" s="1">
         <v>45962</v>
@@ -26485,18 +26593,18 @@
         <v>36</v>
       </c>
       <c r="R536" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="537" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B537" s="5">
         <v>341550943450</v>
       </c>
       <c r="C537" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="D537" t="s">
         <v>352</v>
@@ -26531,13 +26639,13 @@
     </row>
     <row r="538" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B538" s="5">
         <v>307840818390</v>
       </c>
       <c r="C538" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="D538" t="s">
         <v>113</v>
@@ -26572,13 +26680,13 @@
     </row>
     <row r="539" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C539" t="s">
         <v>1240</v>
       </c>
-      <c r="C539" t="s">
+      <c r="D539" t="s">
         <v>1241</v>
-      </c>
-      <c r="D539" t="s">
-        <v>1242</v>
       </c>
       <c r="E539" s="1">
         <v>45962</v>
@@ -26596,7 +26704,7 @@
         <v>7000</v>
       </c>
       <c r="O539" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="P539">
         <v>3798</v>
@@ -26610,16 +26718,16 @@
     </row>
     <row r="540" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B540" s="5">
         <v>308156452068</v>
       </c>
       <c r="C540" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D540" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="E540" s="1">
         <v>45962</v>
@@ -26646,12 +26754,12 @@
         <v>36</v>
       </c>
       <c r="R540" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="541" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C541" t="s">
         <v>643</v>
@@ -26689,16 +26797,16 @@
     </row>
     <row r="542" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B542" s="5">
         <v>343431882988</v>
       </c>
       <c r="C542" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="D542" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E542" s="1">
         <v>45962</v>
@@ -26730,13 +26838,13 @@
     </row>
     <row r="543" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B543" s="5">
         <v>370307823852</v>
       </c>
       <c r="C543" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="D543" t="s">
         <v>153</v>
@@ -26771,16 +26879,16 @@
     </row>
     <row r="544" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="B544" s="5">
         <v>331920553185</v>
       </c>
       <c r="C544" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D544" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E544" s="1">
         <v>45962</v>
@@ -26812,10 +26920,10 @@
     </row>
     <row r="545" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C545" t="s">
         <v>1251</v>
-      </c>
-      <c r="C545" t="s">
-        <v>1252</v>
       </c>
       <c r="D545" t="s">
         <v>113</v>
@@ -26836,7 +26944,7 @@
         <v>56030</v>
       </c>
       <c r="O545" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="P545">
         <v>3815</v>
@@ -26850,10 +26958,10 @@
     </row>
     <row r="546" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C546" t="s">
         <v>1253</v>
-      </c>
-      <c r="C546" t="s">
-        <v>1254</v>
       </c>
       <c r="D546" t="s">
         <v>113</v>
@@ -26874,7 +26982,7 @@
         <v>598320</v>
       </c>
       <c r="O546" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="P546">
         <v>3816</v>
@@ -26888,10 +26996,10 @@
     </row>
     <row r="547" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C547" t="s">
         <v>1255</v>
-      </c>
-      <c r="C547" t="s">
-        <v>1256</v>
       </c>
       <c r="D547" t="s">
         <v>113</v>
@@ -26912,7 +27020,7 @@
         <v>745545</v>
       </c>
       <c r="O547" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="P547">
         <v>3817</v>
@@ -26926,10 +27034,10 @@
     </row>
     <row r="548" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C548" t="s">
         <v>1257</v>
-      </c>
-      <c r="C548" t="s">
-        <v>1258</v>
       </c>
       <c r="D548" t="s">
         <v>113</v>
@@ -26950,7 +27058,7 @@
         <v>9560</v>
       </c>
       <c r="O548" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="P548">
         <v>3818</v>
@@ -26964,10 +27072,10 @@
     </row>
     <row r="549" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C549" t="s">
         <v>1259</v>
-      </c>
-      <c r="C549" t="s">
-        <v>1260</v>
       </c>
       <c r="D549" t="s">
         <v>113</v>
@@ -26988,7 +27096,7 @@
         <v>97460</v>
       </c>
       <c r="O549" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="P549">
         <v>3833</v>
@@ -27002,13 +27110,13 @@
     </row>
     <row r="550" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B550" s="5">
         <v>343439435969</v>
       </c>
       <c r="C550" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="D550" t="s">
         <v>352</v>
@@ -27043,7 +27151,7 @@
     </row>
     <row r="551" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C551" t="s">
         <v>155</v>
@@ -27067,7 +27175,7 @@
         <v>59583</v>
       </c>
       <c r="O551" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="P551">
         <v>1412</v>
@@ -27081,7 +27189,7 @@
     </row>
     <row r="552" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C552" t="s">
         <v>511</v>
@@ -27105,7 +27213,7 @@
         <v>225000</v>
       </c>
       <c r="O552" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="P552">
         <v>634</v>
@@ -27119,16 +27227,16 @@
     </row>
     <row r="553" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B553" s="5">
         <v>307918887146</v>
       </c>
       <c r="C553" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D553" t="s">
         <v>1268</v>
-      </c>
-      <c r="D553" t="s">
-        <v>1269</v>
       </c>
       <c r="E553" s="1">
         <v>45992</v>
@@ -27146,7 +27254,7 @@
         <v>126000</v>
       </c>
       <c r="O553" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="P553">
         <v>3841</v>
@@ -27155,21 +27263,21 @@
         <v>36</v>
       </c>
       <c r="R553" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="554" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B554" s="5">
         <v>307918887146</v>
       </c>
       <c r="C554" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="D554" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="E554" s="1">
         <v>45992</v>
@@ -27187,7 +27295,7 @@
         <v>124000</v>
       </c>
       <c r="O554" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="P554">
         <v>3842</v>
@@ -27196,21 +27304,21 @@
         <v>36</v>
       </c>
       <c r="R554" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="555" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B555" s="5">
         <v>310541952219</v>
       </c>
       <c r="C555" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="D555" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E555" s="1">
         <v>45992</v>
@@ -27242,16 +27350,16 @@
     </row>
     <row r="556" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B556" s="5">
         <v>307833816260</v>
       </c>
       <c r="C556" t="s">
+        <v>1275</v>
+      </c>
+      <c r="D556" t="s">
         <v>1276</v>
-      </c>
-      <c r="D556" t="s">
-        <v>1277</v>
       </c>
       <c r="E556" s="1">
         <v>45992</v>
@@ -27269,7 +27377,7 @@
         <v>105416.1581</v>
       </c>
       <c r="O556" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P556">
         <v>3845</v>
@@ -27278,21 +27386,21 @@
         <v>36</v>
       </c>
       <c r="R556" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="557" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B557" s="5">
         <v>307833816260</v>
       </c>
       <c r="C557" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="D557" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="E557" s="1">
         <v>45992</v>
@@ -27310,7 +27418,7 @@
         <v>148539</v>
       </c>
       <c r="O557" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P557">
         <v>3846</v>
@@ -27319,18 +27427,18 @@
         <v>36</v>
       </c>
       <c r="R557" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="558" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C558" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="D558" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E558" s="1">
         <v>45992</v>
@@ -27362,16 +27470,16 @@
     </row>
     <row r="559" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B559" s="5">
         <v>307814390003</v>
       </c>
       <c r="C559" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D559" t="s">
         <v>1282</v>
-      </c>
-      <c r="D559" t="s">
-        <v>1283</v>
       </c>
       <c r="E559" s="1">
         <v>45992</v>
@@ -27389,7 +27497,7 @@
         <v>50946.096519999999</v>
       </c>
       <c r="O559" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="P559">
         <v>3850</v>
@@ -27398,21 +27506,21 @@
         <v>36</v>
       </c>
       <c r="R559" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="560" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B560" s="5">
         <v>307814390003</v>
       </c>
       <c r="C560" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="D560" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E560" s="1">
         <v>45992</v>
@@ -27430,7 +27538,7 @@
         <v>119873</v>
       </c>
       <c r="O560" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="P560">
         <v>3851</v>
@@ -27439,18 +27547,18 @@
         <v>36</v>
       </c>
       <c r="R560" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="561" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B561" s="5">
         <v>307826006202</v>
       </c>
       <c r="C561" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="D561" t="s">
         <v>342</v>
@@ -27485,13 +27593,13 @@
     </row>
     <row r="562" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B562" s="5">
         <v>307814381778</v>
       </c>
       <c r="C562" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D562" t="s">
         <v>680</v>
@@ -27521,18 +27629,18 @@
         <v>36</v>
       </c>
       <c r="R562" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="563" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B563" s="5">
         <v>307814381778</v>
       </c>
       <c r="C563" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D563" t="s">
         <v>680</v>
@@ -27559,18 +27667,18 @@
         <v>36</v>
       </c>
       <c r="R563" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="564" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="C564" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D564" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E564" s="1">
         <v>45992</v>
@@ -27588,7 +27696,7 @@
         <v>586750</v>
       </c>
       <c r="O564" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="P564">
         <v>3352</v>
@@ -27602,13 +27710,13 @@
     </row>
     <row r="565" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="C565" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D565" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E565" s="1">
         <v>45992</v>
@@ -27626,7 +27734,7 @@
         <v>19053</v>
       </c>
       <c r="O565" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="P565">
         <v>3461</v>
@@ -27640,13 +27748,13 @@
     </row>
     <row r="566" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C566" t="s">
         <v>1295</v>
       </c>
-      <c r="C566" t="s">
-        <v>1296</v>
-      </c>
       <c r="D566" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E566" s="1">
         <v>45992</v>
@@ -27673,12 +27781,12 @@
         <v>36</v>
       </c>
       <c r="R566" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="567" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B567" s="5">
         <v>421037876449</v>
@@ -27719,10 +27827,10 @@
     </row>
     <row r="568" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
+        <v>1297</v>
+      </c>
+      <c r="C568" t="s">
         <v>1298</v>
-      </c>
-      <c r="C568" t="s">
-        <v>1299</v>
       </c>
       <c r="D568" t="s">
         <v>431</v>
@@ -27757,10 +27865,10 @@
     </row>
     <row r="569" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C569" t="s">
         <v>1300</v>
-      </c>
-      <c r="C569" t="s">
-        <v>1301</v>
       </c>
       <c r="D569" t="s">
         <v>431</v>
@@ -27795,10 +27903,10 @@
     </row>
     <row r="570" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C570" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="D570" t="s">
         <v>113</v>
@@ -27833,13 +27941,13 @@
     </row>
     <row r="571" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B571" s="5">
         <v>308003955906</v>
       </c>
       <c r="C571" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="D571" t="s">
         <v>52</v>
@@ -27869,18 +27977,18 @@
         <v>36</v>
       </c>
       <c r="R571" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="572" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
+        <v>1304</v>
+      </c>
+      <c r="C572" t="s">
         <v>1305</v>
       </c>
-      <c r="C572" t="s">
+      <c r="D572" t="s">
         <v>1306</v>
-      </c>
-      <c r="D572" t="s">
-        <v>1307</v>
       </c>
       <c r="E572" s="1">
         <v>45992</v>
@@ -27907,12 +28015,12 @@
         <v>36</v>
       </c>
       <c r="R572" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="573" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B573" s="5">
         <v>322791806200</v>
@@ -27948,12 +28056,12 @@
         <v>36</v>
       </c>
       <c r="R573" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="574" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="C574" t="s">
         <v>139</v>
@@ -27991,7 +28099,7 @@
     </row>
     <row r="575" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="B575" s="5">
         <v>308152808659</v>
@@ -28032,13 +28140,13 @@
     </row>
     <row r="576" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B576" s="5">
         <v>335777842412</v>
       </c>
       <c r="C576" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D576" t="s">
         <v>140</v>
@@ -28068,18 +28176,18 @@
         <v>36</v>
       </c>
       <c r="R576" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="577" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B577" s="5">
         <v>307814381778</v>
       </c>
       <c r="C577" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D577" t="s">
         <v>680</v>
@@ -28109,21 +28217,21 @@
         <v>36</v>
       </c>
       <c r="R577" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="578" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B578" s="5">
         <v>307916942542</v>
       </c>
       <c r="C578" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D578" t="s">
         <v>1315</v>
-      </c>
-      <c r="D578" t="s">
-        <v>1316</v>
       </c>
       <c r="E578" s="1">
         <v>45992</v>
@@ -28141,7 +28249,7 @@
         <v>25500</v>
       </c>
       <c r="O578" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="P578">
         <v>3879</v>
@@ -28150,21 +28258,21 @@
         <v>36</v>
       </c>
       <c r="R578" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="579" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B579" s="5">
         <v>307826006218</v>
       </c>
       <c r="C579" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D579" t="s">
         <v>1319</v>
-      </c>
-      <c r="D579" t="s">
-        <v>1320</v>
       </c>
       <c r="E579" s="1">
         <v>45992</v>
@@ -28182,7 +28290,7 @@
         <v>150000</v>
       </c>
       <c r="O579" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="P579">
         <v>3882</v>
@@ -28196,16 +28304,16 @@
     </row>
     <row r="580" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B580" s="5">
         <v>307826006218</v>
       </c>
       <c r="C580" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="D580" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E580" s="1">
         <v>45992</v>
@@ -28223,7 +28331,7 @@
         <v>150000</v>
       </c>
       <c r="O580" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="P580">
         <v>3884</v>
@@ -28237,10 +28345,10 @@
     </row>
     <row r="581" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C581" t="s">
         <v>1324</v>
-      </c>
-      <c r="C581" t="s">
-        <v>1325</v>
       </c>
       <c r="D581" t="s">
         <v>113</v>
@@ -28261,7 +28369,7 @@
         <v>154380</v>
       </c>
       <c r="O581" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="P581">
         <v>3840</v>
@@ -28275,13 +28383,13 @@
     </row>
     <row r="582" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C582" t="s">
         <v>1326</v>
       </c>
-      <c r="C582" t="s">
+      <c r="D582" t="s">
         <v>1327</v>
-      </c>
-      <c r="D582" t="s">
-        <v>1328</v>
       </c>
       <c r="E582" s="1">
         <v>46023</v>
@@ -28313,13 +28421,13 @@
     </row>
     <row r="583" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C583" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D583" t="s">
         <v>1033</v>
-      </c>
-      <c r="D583" t="s">
-        <v>1034</v>
       </c>
       <c r="E583" s="1">
         <v>45992</v>
@@ -28351,13 +28459,13 @@
     </row>
     <row r="584" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C584" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D584" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E584" s="1">
         <v>45992</v>
@@ -28389,7 +28497,7 @@
     </row>
     <row r="585" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C585" t="s">
         <v>714</v>
@@ -28427,7 +28535,7 @@
     </row>
     <row r="586" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="C586" t="s">
         <v>717</v>
@@ -28465,13 +28573,13 @@
     </row>
     <row r="587" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C587" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="D587" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E587" s="1">
         <v>45992</v>
@@ -28489,7 +28597,7 @@
         <v>25000</v>
       </c>
       <c r="O587" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="P587">
         <v>3662</v>
@@ -28503,7 +28611,7 @@
     </row>
     <row r="588" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="C588" t="s">
         <v>167</v>
@@ -28541,7 +28649,7 @@
     </row>
     <row r="589" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="B589" s="5">
         <v>425090993364</v>
@@ -28568,7 +28676,7 @@
         <v>133301</v>
       </c>
       <c r="O589" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="P589">
         <v>3292</v>
@@ -28582,16 +28690,16 @@
     </row>
     <row r="590" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B590" s="5">
         <v>307842018495</v>
       </c>
       <c r="C590" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D590" t="s">
         <v>1338</v>
-      </c>
-      <c r="D590" t="s">
-        <v>1339</v>
       </c>
       <c r="E590" s="1">
         <v>46023</v>
@@ -28609,7 +28717,7 @@
         <v>74800</v>
       </c>
       <c r="O590" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="P590">
         <v>3892</v>
@@ -28618,21 +28726,21 @@
         <v>36</v>
       </c>
       <c r="R590" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="591" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="B591" s="5">
         <v>389302218999</v>
       </c>
       <c r="C591" t="s">
+        <v>1340</v>
+      </c>
+      <c r="D591" t="s">
         <v>1341</v>
-      </c>
-      <c r="D591" t="s">
-        <v>1342</v>
       </c>
       <c r="E591" s="1">
         <v>46023</v>
@@ -28659,21 +28767,21 @@
         <v>36</v>
       </c>
       <c r="R591" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="592" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B592" s="5">
         <v>307911264460</v>
       </c>
       <c r="C592" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D592" t="s">
         <v>1344</v>
-      </c>
-      <c r="D592" t="s">
-        <v>1345</v>
       </c>
       <c r="E592" s="1">
         <v>46023</v>
@@ -28691,7 +28799,7 @@
         <v>135000</v>
       </c>
       <c r="O592" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="P592">
         <v>3895</v>
@@ -28700,12 +28808,12 @@
         <v>36</v>
       </c>
       <c r="R592" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="593" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C593" t="s">
         <v>29</v>
@@ -28743,7 +28851,7 @@
     </row>
     <row r="594" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B594" s="5">
         <v>307916566765</v>
@@ -28784,13 +28892,13 @@
     </row>
     <row r="595" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C595" t="s">
         <v>1349</v>
       </c>
-      <c r="C595" t="s">
+      <c r="D595" t="s">
         <v>1350</v>
-      </c>
-      <c r="D595" t="s">
-        <v>1351</v>
       </c>
       <c r="E595" s="1">
         <v>46023</v>
@@ -28822,13 +28930,13 @@
     </row>
     <row r="596" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="B596" s="5">
         <v>314262106305</v>
       </c>
       <c r="C596" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D596" t="s">
         <v>113</v>
@@ -28836,7 +28944,7 @@
       <c r="E596" s="1">
         <v>46023</v>
       </c>
-      <c r="F596" t="s">
+      <c r="F596" s="6" t="s">
         <v>21</v>
       </c>
       <c r="G596" t="s">
@@ -28863,21 +28971,21 @@
     </row>
     <row r="597" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="B597" s="5">
         <v>307914457291</v>
       </c>
       <c r="C597" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D597" t="s">
         <v>1355</v>
-      </c>
-      <c r="D597" t="s">
-        <v>1356</v>
       </c>
       <c r="E597" s="1">
         <v>46023</v>
       </c>
-      <c r="F597" t="s">
+      <c r="F597" s="6" t="s">
         <v>34</v>
       </c>
       <c r="G597" t="s">
@@ -28890,7 +28998,7 @@
         <v>400000</v>
       </c>
       <c r="O597" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="P597">
         <v>3903</v>
@@ -28904,18 +29012,18 @@
     </row>
     <row r="598" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C598" t="s">
         <v>1358</v>
       </c>
-      <c r="C598" t="s">
+      <c r="D598" t="s">
         <v>1359</v>
-      </c>
-      <c r="D598" t="s">
-        <v>1360</v>
       </c>
       <c r="E598" s="1">
         <v>46023</v>
       </c>
-      <c r="F598" t="s">
+      <c r="F598" s="6" t="s">
         <v>21</v>
       </c>
       <c r="G598" t="s">
@@ -28940,8 +29048,574 @@
         <v>24</v>
       </c>
     </row>
+    <row r="599" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A599" t="s">
+        <v>1357</v>
+      </c>
+      <c r="C599" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D599" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E599" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F599" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G599" t="s">
+        <v>40</v>
+      </c>
+      <c r="H599">
+        <v>4583.3333333333339</v>
+      </c>
+      <c r="I599">
+        <v>4583.3333333333339</v>
+      </c>
+      <c r="O599" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P599">
+        <v>1522</v>
+      </c>
+      <c r="Q599" t="s">
+        <v>24</v>
+      </c>
+      <c r="R599" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="600" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A600" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C600" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D600" t="s">
+        <v>113</v>
+      </c>
+      <c r="E600" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F600" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G600" t="s">
+        <v>22</v>
+      </c>
+      <c r="H600">
+        <v>794328</v>
+      </c>
+      <c r="J600">
+        <v>794328</v>
+      </c>
+      <c r="O600" s="6" t="s">
+        <v>1196</v>
+      </c>
+      <c r="P600">
+        <v>3630</v>
+      </c>
+      <c r="Q600" t="s">
+        <v>24</v>
+      </c>
+      <c r="R600" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="601" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A601" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C601" t="s">
+        <v>818</v>
+      </c>
+      <c r="D601" t="s">
+        <v>403</v>
+      </c>
+      <c r="E601" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F601" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G601" t="s">
+        <v>22</v>
+      </c>
+      <c r="H601">
+        <v>850000</v>
+      </c>
+      <c r="J601">
+        <v>850000</v>
+      </c>
+      <c r="O601" s="6" t="s">
+        <v>1397</v>
+      </c>
+      <c r="P601">
+        <v>1327</v>
+      </c>
+      <c r="Q601" t="s">
+        <v>24</v>
+      </c>
+      <c r="R601" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="602" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A602" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B602" s="5">
+        <v>307810484425</v>
+      </c>
+      <c r="C602" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D602" t="s">
+        <v>39</v>
+      </c>
+      <c r="E602" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F602" s="6" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G602" t="s">
+        <v>40</v>
+      </c>
+      <c r="H602">
+        <v>168000</v>
+      </c>
+      <c r="I602">
+        <v>168000</v>
+      </c>
+      <c r="O602" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="P602">
+        <v>2399</v>
+      </c>
+      <c r="Q602" t="s">
+        <v>36</v>
+      </c>
+      <c r="R602" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="603" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A603" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B603" s="5">
+        <v>307810484425</v>
+      </c>
+      <c r="C603" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D603" t="s">
+        <v>39</v>
+      </c>
+      <c r="E603" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F603" s="6" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G603" t="s">
+        <v>22</v>
+      </c>
+      <c r="H603">
+        <v>175000</v>
+      </c>
+      <c r="J603">
+        <v>175000</v>
+      </c>
+      <c r="O603" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="P603">
+        <v>2400</v>
+      </c>
+      <c r="Q603" t="s">
+        <v>36</v>
+      </c>
+      <c r="R603" t="s">
+        <v>1368</v>
+      </c>
+    </row>
+    <row r="604" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A604" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B604" s="5">
+        <v>425898569927</v>
+      </c>
+      <c r="C604" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D604" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E604" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F604" s="6" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G604" t="s">
+        <v>40</v>
+      </c>
+      <c r="H604">
+        <v>165025</v>
+      </c>
+      <c r="I604">
+        <v>165025</v>
+      </c>
+      <c r="O604" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="P604">
+        <v>3918</v>
+      </c>
+      <c r="Q604" t="s">
+        <v>36</v>
+      </c>
+      <c r="R604" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="605" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A605" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B605" s="5">
+        <v>425898569927</v>
+      </c>
+      <c r="C605" t="s">
+        <v>1386</v>
+      </c>
+      <c r="D605" t="s">
+        <v>1393</v>
+      </c>
+      <c r="E605" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F605" s="6" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G605" t="s">
+        <v>22</v>
+      </c>
+      <c r="H605">
+        <v>156950</v>
+      </c>
+      <c r="J605">
+        <v>156950</v>
+      </c>
+      <c r="O605" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="P605">
+        <v>3919</v>
+      </c>
+      <c r="Q605" t="s">
+        <v>36</v>
+      </c>
+      <c r="R605" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="606" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A606" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B606" s="5">
+        <v>389302218999</v>
+      </c>
+      <c r="C606" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D606" t="s">
+        <v>1341</v>
+      </c>
+      <c r="E606" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F606" s="6" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G606" t="s">
+        <v>22</v>
+      </c>
+      <c r="H606">
+        <v>210990.95102921451</v>
+      </c>
+      <c r="J606">
+        <v>210990.95102921451</v>
+      </c>
+      <c r="O606" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="P606">
+        <v>3920</v>
+      </c>
+      <c r="Q606" t="s">
+        <v>36</v>
+      </c>
+      <c r="R606" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="607" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A607" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B607" s="5">
+        <v>309329834226</v>
+      </c>
+      <c r="C607" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D607" t="s">
+        <v>1350</v>
+      </c>
+      <c r="E607" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F607" s="6" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G607" t="s">
+        <v>40</v>
+      </c>
+      <c r="H607">
+        <v>70000</v>
+      </c>
+      <c r="I607">
+        <v>70000</v>
+      </c>
+      <c r="O607" t="s">
+        <v>1398</v>
+      </c>
+      <c r="P607">
+        <v>3924</v>
+      </c>
+      <c r="Q607" t="s">
+        <v>36</v>
+      </c>
+      <c r="R607" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="608" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A608" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B608" s="5">
+        <v>455558275296</v>
+      </c>
+      <c r="C608" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D608" t="s">
+        <v>153</v>
+      </c>
+      <c r="E608" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F608" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G608" t="s">
+        <v>22</v>
+      </c>
+      <c r="H608">
+        <v>450000</v>
+      </c>
+      <c r="J608">
+        <v>450000</v>
+      </c>
+      <c r="O608" s="6" t="s">
+        <v>1263</v>
+      </c>
+      <c r="P608">
+        <v>3926</v>
+      </c>
+      <c r="Q608" t="s">
+        <v>24</v>
+      </c>
+      <c r="R608" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="609" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A609" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B609" s="5">
+        <v>307826010341</v>
+      </c>
+      <c r="C609" t="s">
+        <v>1390</v>
+      </c>
+      <c r="D609" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E609" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F609" s="6" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G609" t="s">
+        <v>40</v>
+      </c>
+      <c r="H609">
+        <v>300000</v>
+      </c>
+      <c r="I609">
+        <v>300000</v>
+      </c>
+      <c r="O609" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="P609">
+        <v>3933</v>
+      </c>
+      <c r="Q609" t="s">
+        <v>62</v>
+      </c>
+      <c r="R609" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="610" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A610" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B610" s="5">
+        <v>307826010341</v>
+      </c>
+      <c r="C610" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D610" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E610" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F610" s="6" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G610" t="s">
+        <v>22</v>
+      </c>
+      <c r="H610">
+        <v>100000</v>
+      </c>
+      <c r="J610">
+        <v>100000</v>
+      </c>
+      <c r="O610" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="P610">
+        <v>3934</v>
+      </c>
+      <c r="Q610" t="s">
+        <v>62</v>
+      </c>
+      <c r="R610" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="611" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A611" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B611" s="5">
+        <v>308190613738</v>
+      </c>
+      <c r="C611" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D611" t="s">
+        <v>388</v>
+      </c>
+      <c r="E611" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F611" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G611" t="s">
+        <v>22</v>
+      </c>
+      <c r="H611">
+        <v>40000</v>
+      </c>
+      <c r="J611">
+        <v>40000</v>
+      </c>
+      <c r="O611" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P611">
+        <v>3935</v>
+      </c>
+      <c r="Q611" t="s">
+        <v>24</v>
+      </c>
+      <c r="R611" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="612" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A612" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C612" t="s">
+        <v>167</v>
+      </c>
+      <c r="D612" t="s">
+        <v>168</v>
+      </c>
+      <c r="E612" s="1">
+        <v>46054</v>
+      </c>
+      <c r="F612" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G612" t="s">
+        <v>22</v>
+      </c>
+      <c r="H612">
+        <v>-721654.14285714284</v>
+      </c>
+      <c r="J612">
+        <v>-721654.14285714284</v>
+      </c>
+      <c r="O612" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="P612">
+        <v>1991</v>
+      </c>
+      <c r="Q612" t="s">
+        <v>24</v>
+      </c>
+      <c r="R612" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R598" xr:uid="{445A7FF1-69C5-4B51-B3A2-42A65126DD1A}"/>
+  <autoFilter ref="A1:R612" xr:uid="{445A7FF1-69C5-4B51-B3A2-42A65126DD1A}"/>
+  <conditionalFormatting sqref="A599:A612">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/backend/data/closed_acv.xlsx
+++ b/backend/data/closed_acv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gep1-my.sharepoint.com/personal/ajoseph_gep_com/Documents/Desktop/Project-Aether-Enterprise/backend/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="147" documentId="8_{E886ED90-0776-4F81-A4C1-54B160D1665C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53F42021-D1B9-4948-BEEF-0D806D122B17}"/>
+  <xr:revisionPtr revIDLastSave="166" documentId="8_{E886ED90-0776-4F81-A4C1-54B160D1665C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B07EDD5A-B696-4406-9D7B-BC8D9F77B9DD}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{362E1928-A501-4CAC-8243-2F29D3895462}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4931" uniqueCount="1399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4931" uniqueCount="1397">
   <si>
     <t>Closed_ACV_ID</t>
   </si>
@@ -4224,12 +4224,6 @@
   </si>
   <si>
     <t>Logitech Europe S.A</t>
-  </si>
-  <si>
-    <t>CrossSell</t>
-  </si>
-  <si>
-    <t>New</t>
   </si>
   <si>
     <t>Johnson Fernandez</t>
@@ -5132,6 +5126,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="19" customWidth="1"/>
     <col min="18" max="18" width="18.90625" bestFit="1" customWidth="1"/>
   </cols>
@@ -17049,7 +17044,7 @@
         <v>155000</v>
       </c>
       <c r="O297" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="P297">
         <v>3337</v>
@@ -17087,7 +17082,7 @@
         <v>165000</v>
       </c>
       <c r="O298" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="P298">
         <v>3338</v>
@@ -28985,7 +28980,7 @@
       <c r="E597" s="1">
         <v>46023</v>
       </c>
-      <c r="F597" s="6" t="s">
+      <c r="F597" t="s">
         <v>34</v>
       </c>
       <c r="G597" t="s">
@@ -29150,7 +29145,7 @@
         <v>850000</v>
       </c>
       <c r="O601" s="6" t="s">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="P601">
         <v>1327</v>
@@ -29178,8 +29173,8 @@
       <c r="E602" s="1">
         <v>46054</v>
       </c>
-      <c r="F602" s="6" t="s">
-        <v>1395</v>
+      <c r="F602" t="s">
+        <v>126</v>
       </c>
       <c r="G602" t="s">
         <v>40</v>
@@ -29219,8 +29214,8 @@
       <c r="E603" s="1">
         <v>46054</v>
       </c>
-      <c r="F603" s="6" t="s">
-        <v>1395</v>
+      <c r="F603" t="s">
+        <v>126</v>
       </c>
       <c r="G603" t="s">
         <v>22</v>
@@ -29260,8 +29255,8 @@
       <c r="E604" s="1">
         <v>46054</v>
       </c>
-      <c r="F604" s="6" t="s">
-        <v>1396</v>
+      <c r="F604" t="s">
+        <v>34</v>
       </c>
       <c r="G604" t="s">
         <v>40</v>
@@ -29301,8 +29296,8 @@
       <c r="E605" s="1">
         <v>46054</v>
       </c>
-      <c r="F605" s="6" t="s">
-        <v>1396</v>
+      <c r="F605" t="s">
+        <v>34</v>
       </c>
       <c r="G605" t="s">
         <v>22</v>
@@ -29342,8 +29337,8 @@
       <c r="E606" s="1">
         <v>46054</v>
       </c>
-      <c r="F606" s="6" t="s">
-        <v>1396</v>
+      <c r="F606" t="s">
+        <v>34</v>
       </c>
       <c r="G606" t="s">
         <v>22</v>
@@ -29383,8 +29378,8 @@
       <c r="E607" s="1">
         <v>46054</v>
       </c>
-      <c r="F607" s="6" t="s">
-        <v>1395</v>
+      <c r="F607" t="s">
+        <v>126</v>
       </c>
       <c r="G607" t="s">
         <v>40</v>
@@ -29396,7 +29391,7 @@
         <v>70000</v>
       </c>
       <c r="O607" t="s">
-        <v>1398</v>
+        <v>1396</v>
       </c>
       <c r="P607">
         <v>3924</v>
@@ -29465,8 +29460,8 @@
       <c r="E609" s="1">
         <v>46054</v>
       </c>
-      <c r="F609" s="6" t="s">
-        <v>1396</v>
+      <c r="F609" t="s">
+        <v>34</v>
       </c>
       <c r="G609" t="s">
         <v>40</v>
@@ -29506,8 +29501,8 @@
       <c r="E610" s="1">
         <v>46054</v>
       </c>
-      <c r="F610" s="6" t="s">
-        <v>1396</v>
+      <c r="F610" t="s">
+        <v>34</v>
       </c>
       <c r="G610" t="s">
         <v>22</v>
